--- a/clean/aea_listings_2026-10-15.xlsx
+++ b/clean/aea_listings_2026-10-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M119"/>
+  <dimension ref="A1:M114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3309,23 +3309,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Beijing Normal University</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
+          <t>Capital University of Economics and Business</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Business School</t>
+          <t>International School of Economics and Management</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=96DC1B7F3204BD16</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=230A8F8CAE8FB702</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3335,7 +3331,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=96DC1B7F3204BD16</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=230A8F8CAE8FB702</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3352,19 +3348,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Capital University of Economics and Business</t>
+          <t>Dongbei University of Finance &amp; Economics</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>International School of Economics and Management</t>
+          <t>Dongbei University Of Finance And Economics</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=230A8F8CAE8FB702</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=9058523321C2911A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3374,7 +3370,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=230A8F8CAE8FB702</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=9058523321C2911A</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3391,19 +3387,23 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dongbei University of Finance &amp; Economics</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>Donghua University</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dongbei University Of Finance And Economics</t>
+          <t>Glorious Sun School of Business and Management</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=9058523321C2911A</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=1CE68DDB85B84365</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=9058523321C2911A</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=1CE68DDB85B84365</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3430,23 +3430,26 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Donghua University</t>
+          <t>Fudan University</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>985/211</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Glorious Sun School of Business and Management</t>
-        </is>
+          <t>School of Economics</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>46327</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=1CE68DDB85B84365</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=E968D280DD59D564</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3456,7 +3459,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=1CE68DDB85B84365</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=E968D280DD59D564</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3483,16 +3486,18 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>School of Economics</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="n">
-        <v>46327</v>
+          <t>School of Management</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=E968D280DD59D564</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=E153FEE8CC8E11B5</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3502,7 +3507,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=E968D280DD59D564</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=E153FEE8CC8E11B5</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3519,28 +3524,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fudan University</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
+          <t>Harbin Institute of Technology</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>School of Management</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Rolling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=E153FEE8CC8E11B5</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3ED8A58471D2F80B</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3550,7 +3546,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=E153FEE8CC8E11B5</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3ED8A58471D2F80B</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -3567,19 +3563,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Harbin Institute of Technology</t>
+          <t>Huazhong University of Science and Technology</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>School of Management</t>
+          <t>School of Economics, Huazhong University of Science &amp; Technology</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3ED8A58471D2F80B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A380FA8882023C78</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>CV; Job Market Paper; Letters of Reference</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3589,7 +3590,7 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3ED8A58471D2F80B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A380FA8882023C78</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -3606,24 +3607,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Huazhong University of Science and Technology</t>
+          <t>Hunan University</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>School of Economics, Huazhong University of Science &amp; Technology</t>
+          <t>School of Economics and Trade</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A380FA8882023C78</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>CV; Job Market Paper; Letters of Reference</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=38CE3CA2770AB83B</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3633,7 +3629,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A380FA8882023C78</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=38CE3CA2770AB83B</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -3650,19 +3646,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hunan University</t>
+          <t>Jilin University</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>School of Economics and Trade</t>
+          <t>Business School</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=38CE3CA2770AB83B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A4E054BFC7078E2F</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3672,7 +3668,7 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=38CE3CA2770AB83B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A4E054BFC7078E2F</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -3689,19 +3685,19 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jilin University</t>
+          <t>Lanzhou University of Finance and Economics</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Business School</t>
+          <t>the Office of Personnel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A4E054BFC7078E2F</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=003923B6EFE42FFF</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3711,7 +3707,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A4E054BFC7078E2F</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=003923B6EFE42FFF</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -3728,19 +3724,23 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Lanzhou University of Finance and Economics</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>Nanjing Agricultural University</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>985/211</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>the Office of Personnel</t>
+          <t>College of Finance</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=003923B6EFE42FFF</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=41CE1E8D1AE20F34</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=003923B6EFE42FFF</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=41CE1E8D1AE20F34</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Nanjing Agricultural University</t>
+          <t>Nanjing University</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3777,13 +3777,13 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>College of Finance</t>
+          <t>Business School</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=41CE1E8D1AE20F34</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=5EE87D5DE6734D4D</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=41CE1E8D1AE20F34</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=5EE87D5DE6734D4D</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Nanjing University</t>
+          <t>Nankai University</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3820,13 +3820,13 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Business School</t>
+          <t>School of Finance</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=5EE87D5DE6734D4D</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=96728BEC2B0A48B6</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=5EE87D5DE6734D4D</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=96728BEC2B0A48B6</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Nankai University</t>
+          <t>Peking University</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3863,13 +3863,16 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>School of Finance</t>
-        </is>
+          <t>Peking University HSBC Business School</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>46364</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=96728BEC2B0A48B6</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3879,7 +3882,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=96728BEC2B0A48B6</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -3906,16 +3909,18 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Peking University HSBC Business School</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="n">
-        <v>46364</v>
+          <t>Guanghua School of Management</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3925,7 +3930,7 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -3942,7 +3947,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Peking University</t>
+          <t>Renmin University of China</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3952,18 +3957,16 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Guanghua School of Management</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Rolling</t>
-        </is>
+          <t>School of Finance, Renmin University of China</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>46357</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3973,7 +3976,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -3990,19 +3993,26 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remin University</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>Shanghai Jiao Tong University</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>School of Applied Economics</t>
-        </is>
+          <t>Antai College of Economics and Management</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>46341</v>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=680004BD3C688FB5</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4012,7 +4022,7 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=680004BD3C688FB5</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -4029,26 +4039,23 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Renmin University of China</t>
+          <t>Shanghai University of Finance Economics School</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>985/211</t>
+          <t>211</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>School of Finance, Renmin University of China</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="n">
-        <v>46357</v>
+          <t>School of Digital Economy</t>
+        </is>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=7E509CEAE1E65959</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4058,7 +4065,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=7E509CEAE1E65959</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -4075,7 +4082,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Shanghai Jiao Tong University</t>
+          <t>Shanghai University of Finance and Economics</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4085,16 +4092,13 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Antai College of Economics and Management</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="n">
-        <v>46341</v>
+          <t>School of Economics</t>
+        </is>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4104,7 +4108,7 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -4121,23 +4125,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Shanghai University of Finance Economics School</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
+          <t>Southwestern University of Finance and Economics</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>School of Digital Economy</t>
+          <t>School of Economics</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=7E509CEAE1E65959</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=8F2A4E7B41A62BEC</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=7E509CEAE1E65959</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=8F2A4E7B41A62BEC</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -4164,23 +4164,26 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Shanghai University of Finance and Economics</t>
+          <t>Tsinghua University</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>985/211</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>School of Economics</t>
-        </is>
+          <t>School of Economics and Management</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>46356</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4190,7 +4193,7 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -4207,23 +4210,23 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Shanghai University of Finance and Economics</t>
+          <t>Tsinghua University</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>985/211</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dishui Lake Advanced Finance Institute</t>
+          <t>Center for International Finance and Economics Research</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=5D5B5B1874A95B18</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4233,7 +4236,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=5D5B5B1874A95B18</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -4250,19 +4253,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Southwestern University of Finance and Economics</t>
+          <t>University of Electronic Science and Technology of China</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>School of Economics</t>
+          <t>School of Management and Economics</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=8F2A4E7B41A62BEC</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4272,7 +4275,7 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=8F2A4E7B41A62BEC</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -4289,23 +4292,19 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tongji University</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
+          <t>University of Science and Technology of China</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>nothing</t>
+          <t>Institute of International Finance</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=41EFAE6DC817CCD8</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4315,7 +4314,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=41EFAE6DC817CCD8</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -4332,26 +4331,19 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tsinghua University</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
+          <t>University of Science and Technology of China</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>School of Economics and Management</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="n">
-        <v>46356</v>
+          <t>School of Management</t>
+        </is>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4361,7 +4353,7 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -4378,23 +4370,19 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tsinghua University</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
+          <t>Xi%u2019an Jiaotong University</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>School of Social Sciences</t>
+          <t>School of Economics and Finance</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=48673CE5E9319FD6</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4404,7 +4392,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=48673CE5E9319FD6</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -4421,23 +4409,19 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tsinghua University</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
+          <t>Xi%u2019an Jiaotong-Liverpool University</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Center for International Finance and Economics Research</t>
+          <t>International Business School Suzhou (IBSS), Department of Economics</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4447,7 +4431,7 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -4464,19 +4448,23 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>University of Electronic Science and Technology of China</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>Zhejiang University</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>985/211</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>School of Management and Economics</t>
+          <t>International Business School</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4486,7 +4474,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -4503,19 +4491,19 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>University of Science and Technology of China</t>
+          <t>Zhongnan Unviersity of Economics and Law</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Institute of International Finance</t>
+          <t>School of Finance</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4525,7 +4513,7 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -4537,34 +4525,52 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Kowloon Tong, Kowloon</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>University of Science and Technology of China</t>
+          <t>City University of Hong Kong</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>School of Management</t>
-        </is>
+          <t>Economics and Finance</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>46356</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
+          <t>https://econjobmarket.org/positions/12596</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Job Market Paper; Research Statement</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>CICE</t>
+          <t>EJM</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
+          <t>https://econjobmarket.org/positions/12596</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>efpost@cityu.edu.hk</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -4576,34 +4582,47 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Pokfulam Road</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Xi%u2019an Jiaotong University</t>
+          <t>University of Hong Kong</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>School of Economics and Finance</t>
-        </is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>46341</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
+          <t>https://econjobmarket.org/positions/12521</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>CICE</t>
+          <t>EJM</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
+          <t>https://econjobmarket.org/positions/12521</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>orgecon@hku.hk</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -4615,34 +4634,52 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Pokfulam Road</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Xi%u2019an Jiaotong-Liverpool University</t>
+          <t>University of Hong Kong</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>International Business School Suzhou (IBSS), Department of Economics</t>
-        </is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>46356</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
+          <t>https://econjobmarket.org/positions/12581</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Job Market Paper</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>CICE</t>
+          <t>EJM</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
+          <t>https://econjobmarket.org/positions/12581</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>econ.jobmarket@hku.hk</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -4654,38 +4691,51 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Zhejiang University</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
+          <t>City University of Hong Kong</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>International Business School</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr"/>
+          <t>Department of Economics and Finance</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>46356</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477722 | http://jobs.cityu.edu.hk</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Job Market Paper; Research Statement</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>CICE</t>
+          <t>AEA</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
+          <t>http://jobs.cityu.edu.hk</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>efpost@cityu.edu.hk</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -4697,34 +4747,51 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Zhongnan Unviersity of Economics and Law</t>
+          <t>City University of Hong Kong</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>School of Finance</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr"/>
+          <t>Department of Economics and Finance</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>46356</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477723 | http://jobs.cityu.edu.hk</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Job Market Paper; Research Statement</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>CICE</t>
+          <t>AEA</t>
         </is>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
+          <t>http://jobs.cityu.edu.hk</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>efpost@cityu.edu.hk</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -4736,12 +4803,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Kowloon Tong, Kowloon</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4750,38 +4812,27 @@
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Economics and Finance</t>
-        </is>
-      </c>
       <c r="F86" s="2" t="n">
-        <v>46356</v>
-      </c>
-      <c r="G86" t="inlineStr"/>
+        <v>46418</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12596</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>Job Market Paper; Research Statement</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477624 | https://www.cityu.edu.hk/academic/colleges-schools-and-departments</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>EJM</t>
+          <t>AEA</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12596</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>efpost@cityu.edu.hk</t>
+          <t>https://www.cityu.edu.hk/academic/colleges-schools-and-departments</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -4793,17 +4844,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Pokfulam Road</t>
+          <t>Hong Kong, Hong Kong</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>University of Hong Kong</t>
+          <t>Hong Kong University of Science and Technology</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -4813,27 +4864,36 @@
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>46341</v>
-      </c>
-      <c r="G87" t="inlineStr"/>
+        <v>46348</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12521</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477656 | https://apply.interfolio.com/191029</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Research Papers</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>EJM</t>
+          <t>AEA</t>
         </is>
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12521</t>
+          <t>https://apply.interfolio.com/191029</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>orgecon@hku.hk</t>
+          <t>econjob@ust.hk</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -4845,52 +4905,51 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Pokfulam Road</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>University of Hong Kong</t>
+          <t>The Chinese University of Hong Kong</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Economics</t>
+          <t>Department of Decisions, Operations and Technology</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
-        <v>46356</v>
-      </c>
-      <c r="G88" t="inlineStr"/>
+        <v>46387</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12581</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477636 | http://career.cuhk.edu.hk</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Job Market Paper</t>
+          <t>Teaching Evaluations</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>EJM</t>
+          <t>AEA</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12581</t>
+          <t>http://career.cuhk.edu.hk</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>econ.jobmarket@hku.hk</t>
+          <t>dote@cuhk.edu.hk</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -4907,13 +4966,13 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>City University of Hong Kong</t>
+          <t>The University of Hong Kong</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Department of Economics and Finance</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F89" s="2" t="n">
@@ -4926,12 +4985,12 @@
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477722 | http://jobs.cityu.edu.hk</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477668 | https://jobs.hku.hk</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Job Market Paper; Research Statement</t>
+          <t>Job Market Paper</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -4941,12 +5000,12 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>http://jobs.cityu.edu.hk</t>
+          <t>https://jobs.hku.hk</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>efpost@cityu.edu.hk</t>
+          <t>econ.jobmarket@hku.hk</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -4958,18 +5017,23 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>JAPAN</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Tokyo, Tokyo</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>City University of Hong Kong</t>
+          <t>Bank of Japan</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Department of Economics and Finance</t>
+          <t>Institute for Monetary and Economic Studies (IMES)</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
@@ -4982,12 +5046,12 @@
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477723 | http://jobs.cityu.edu.hk</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477873</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Job Market Paper; Research Statement</t>
+          <t>Research Papers</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -4997,12 +5061,7 @@
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>http://jobs.cityu.edu.hk</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>efpost@cityu.edu.hk</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477873</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -5014,12 +5073,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>JAPAN</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Minato-Ku, Tokyo</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>City University of Hong Kong</t>
+          <t>Japan Fair Trade Commission</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -5033,7 +5097,12 @@
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477624 | https://www.cityu.edu.hk/academic/colleges-schools-and-departments</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477599 | https://www.jftc.go.jp/soshiki/recruit/specialty.html</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Research Papers</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5043,7 +5112,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>https://www.cityu.edu.hk/academic/colleges-schools-and-departments</t>
+          <t>https://www.jftc.go.jp/soshiki/recruit/specialty.html</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -5055,17 +5124,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>JAPAN</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Hong Kong, Hong Kong</t>
+          <t>Tokyo, Tokyo</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hong Kong University of Science and Technology</t>
+          <t>Musashi University</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -5075,7 +5144,7 @@
         </is>
       </c>
       <c r="F92" s="2" t="n">
-        <v>46348</v>
+        <v>46326</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -5084,12 +5153,7 @@
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477656 | https://apply.interfolio.com/191029</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>Research Papers</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477561 | https://jrecin.jst.go.jp/seek/SeekJorDetail/Changelang?id=D126070158&amp;lang=1</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5099,12 +5163,7 @@
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>https://apply.interfolio.com/191029</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>econjob@ust.hk</t>
+          <t>https://jrecin.jst.go.jp/seek/SeekJorDetail/Changelang?id=D126070158&amp;lang=1</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -5116,22 +5175,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>JAPAN</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Yushima, Bunkyo, Tokyo</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>The Chinese University of Hong Kong</t>
+          <t>UTokyo Economic Consulting Inc.</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Department of Decisions, Operations and Technology</t>
-        </is>
-      </c>
       <c r="F93" s="2" t="n">
-        <v>46387</v>
+        <v>46356</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -5140,12 +5199,7 @@
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477636 | http://career.cuhk.edu.hk</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>Teaching Evaluations</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477714 | https://utecon.net/en/</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5155,12 +5209,12 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>http://career.cuhk.edu.hk</t>
+          <t>https://utecon.net/en/</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>dote@cuhk.edu.hk</t>
+          <t>recruit@utecon.net</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -5172,22 +5226,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>JAPAN</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>The University of Hong Kong</t>
+          <t>Waseda University</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Economics</t>
-        </is>
-      </c>
       <c r="F94" s="2" t="n">
-        <v>46356</v>
+        <v>46310</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -5196,12 +5250,7 @@
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477668 | https://jobs.hku.hk</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>Job Market Paper</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477611 | https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26944/</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5211,12 +5260,7 @@
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.hku.hk</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>econ.jobmarket@hku.hk</t>
+          <t>https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26944/</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -5233,22 +5277,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Tokyo, Tokyo</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bank of Japan</t>
+          <t>Waseda University</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Institute for Monetary and Economic Studies (IMES)</t>
+          <t>Faculty of Political Science and Economics (FPSE)</t>
         </is>
       </c>
       <c r="F95" s="2" t="n">
-        <v>46356</v>
+        <v>46310</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -5257,12 +5301,7 @@
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477873</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Research Papers</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477612 | https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26955/</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5272,7 +5311,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477873</t>
+          <t>https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26955/</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -5284,31 +5323,32 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>JAPAN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Minato-Ku, Tokyo</t>
+          <t>Kyoto, Kyoto</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Japan Fair Trade Commission</t>
+          <t>Kyoto University</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Institute for Economic Research</t>
+        </is>
+      </c>
       <c r="F96" s="2" t="n">
-        <v>46418</v>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+        <v>46332</v>
+      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477599 | https://www.jftc.go.jp/soshiki/recruit/specialty.html</t>
+          <t>https://econjobmarket.org/positions/12683</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5318,12 +5358,17 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>AEA</t>
+          <t>EJM</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>https://www.jftc.go.jp/soshiki/recruit/specialty.html</t>
+          <t>https://econjobmarket.org/positions/12683</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>soumu-jinji@kier.kyoto-u.ac.jp</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -5335,27 +5380,19 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>JAPAN</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Tokyo, Tokyo</t>
+          <t>MACAO; CHINA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Musashi University</t>
+          <t>University of Macau (UM)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Economics</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="n">
-        <v>46326</v>
+          <t>Department of Finance and Business Economics</t>
+        </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -5364,7 +5401,12 @@
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477561 | https://jrecin.jst.go.jp/seek/SeekJorDetail/Changelang?id=D126070158&amp;lang=1</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477678 | https://career.admo.um.edu.mo/learn-more</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>CV; Cover Letter; Job Market Paper; Research Papers; Teaching Evaluations; Letters of Reference</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5374,7 +5416,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>https://jrecin.jst.go.jp/seek/SeekJorDetail/Changelang?id=D126070158&amp;lang=1</t>
+          <t>https://career.admo.um.edu.mo/learn-more</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -5386,46 +5428,47 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>JAPAN</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Yushima, Bunkyo, Tokyo</t>
+          <t>Kuala Lumpur, Malaysia</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>UTokyo Economic Consulting Inc.</t>
+          <t>Asia School of Business</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>All departments</t>
+        </is>
+      </c>
       <c r="F98" s="2" t="n">
         <v>46356</v>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477714 | https://utecon.net/en/</t>
+          <t>https://econjobmarket.org/positions/12494</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>CV; Teaching Statement</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>AEA</t>
+          <t>EJM</t>
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>https://utecon.net/en/</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>recruit@utecon.net</t>
+          <t>https://econjobmarket.org/positions/12494</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -5437,22 +5480,27 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>JAPAN</t>
+          <t>NEW ZEALAND</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Auckland, Auckland</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Waseda University</t>
+          <t>The University of Auckland</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
       <c r="F99" s="2" t="n">
-        <v>46310</v>
+        <v>46321</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -5461,7 +5509,12 @@
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477611 | https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26944/</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478084 | https://jobs.smartrecruiters.com/TheUniversityOfAuckland/744000151521321-lecturer-senior-lecturer-economics</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>CV; Cover Letter; Teaching Evaluations</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5471,7 +5524,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26944/</t>
+          <t>https://jobs.smartrecruiters.com/TheUniversityOfAuckland/744000151521321-lecturer-senior-lecturer-economics</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -5483,27 +5536,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>JAPAN</t>
+          <t>TAIWAN</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Taipei</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Waseda University</t>
+          <t>Institute of Economics, Academia Sinica (IEAS)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Faculty of Political Science and Economics (FPSE)</t>
-        </is>
-      </c>
       <c r="F100" s="2" t="n">
-        <v>46310</v>
+        <v>46357</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -5512,7 +5560,12 @@
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477612 | https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26955/</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477843 | https://www.econ.sinica.edu.tw/</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Cover Letter; Job Market Paper</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5522,7 +5575,12 @@
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26955/</t>
+          <t>https://www.econ.sinica.edu.tw/</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>searchcommit@econ.sinica.edu.tw</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -5534,52 +5592,56 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TAIWAN</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Kyoto, Kyoto</t>
+          <t>Taoyuan</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Kyoto University</t>
+          <t>National Central University</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Institute for Economic Research</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F101" s="2" t="n">
-        <v>46332</v>
-      </c>
-      <c r="G101" t="inlineStr"/>
+        <v>46358</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12683</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477598</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Research Papers</t>
+          <t>CV; Cover Letter; Job Market Paper; Transcript</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>EJM</t>
+          <t>AEA</t>
         </is>
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12683</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477598</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>soumu-jinji@kier.kyoto-u.ac.jp</t>
+          <t>ncu66301@ncu.edu.tw</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -5591,19 +5653,27 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MACAO; CHINA</t>
+          <t>TAIWAN</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Zhongli, Taoyuan</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>University of Macau (UM)</t>
+          <t>National Central University</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Department of Finance and Business Economics</t>
-        </is>
+          <t>Graduate Institute of Industrial Economics</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>46368</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -5612,12 +5682,7 @@
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477678 | https://career.admo.um.edu.mo/learn-more</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>CV; Cover Letter; Job Market Paper; Research Papers; Teaching Evaluations; Letters of Reference</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477690</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -5627,7 +5692,7 @@
       </c>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>https://career.admo.um.edu.mo/learn-more</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477690</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -5639,47 +5704,56 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>TAIWAN</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Kuala Lumpur, Malaysia</t>
+          <t>Taoyuan City</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Asia School of Business</t>
+          <t>National Central University</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>All departments</t>
+          <t>Department of Finance</t>
         </is>
       </c>
       <c r="F103" s="2" t="n">
-        <v>46356</v>
-      </c>
-      <c r="G103" t="inlineStr"/>
+        <v>46402</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12494</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477637</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>CV; Teaching Statement</t>
+          <t>Job Market Paper</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>EJM</t>
+          <t>AEA</t>
         </is>
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12494</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477637</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>ncu6250@ncu.edu.tw</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -5691,17 +5765,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>NEW ZEALAND</t>
+          <t>TAIWAN</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Auckland, Auckland</t>
+          <t>Tainan</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>The University of Auckland</t>
+          <t>National Cheng Kung University</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -5711,7 +5785,7 @@
         </is>
       </c>
       <c r="F104" s="2" t="n">
-        <v>46321</v>
+        <v>46354</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -5720,12 +5794,12 @@
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478084 | https://jobs.smartrecruiters.com/TheUniversityOfAuckland/744000151521321-lecturer-senior-lecturer-economics</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477925</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>CV; Cover Letter; Teaching Evaluations</t>
+          <t>Cover Letter</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -5735,7 +5809,7 @@
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/TheUniversityOfAuckland/744000151521321-lecturer-senior-lecturer-economics</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477925</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -5757,12 +5831,17 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Institute of Economics, Academia Sinica (IEAS)</t>
+          <t>National Chengchi University</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Department of Economics</t>
+        </is>
+      </c>
       <c r="F105" s="2" t="n">
-        <v>46357</v>
+        <v>46356</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -5771,12 +5850,7 @@
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477843 | https://www.econ.sinica.edu.tw/</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>Cover Letter; Job Market Paper</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477745</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -5786,12 +5860,12 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>https://www.econ.sinica.edu.tw/</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477745</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>searchcommit@econ.sinica.edu.tw</t>
+          <t>econ@nccu.edu.tw</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -5808,22 +5882,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Taoyuan</t>
+          <t>Taipei</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>National Central University</t>
+          <t>National Chengchi University</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Economics</t>
+          <t>College of Global Banking and Finance</t>
         </is>
       </c>
       <c r="F106" s="2" t="n">
-        <v>46358</v>
+        <v>46387</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -5832,12 +5906,12 @@
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477598</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477791 | https://cgbf.nccu.edu.tw/</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>CV; Cover Letter; Job Market Paper; Transcript</t>
+          <t>CV; Job Market Paper</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -5847,12 +5921,12 @@
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477598</t>
+          <t>https://cgbf.nccu.edu.tw/</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>ncu66301@ncu.edu.tw</t>
+          <t>pthung@mail3.nccu.tw</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -5869,22 +5943,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Zhongli, Taoyuan</t>
+          <t>Taipei</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>National Central University</t>
+          <t>National Chengchi University</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Graduate Institute of Industrial Economics</t>
+          <t>Department of Money and Banking</t>
         </is>
       </c>
       <c r="F107" s="2" t="n">
-        <v>46368</v>
+        <v>46418</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -5893,7 +5967,12 @@
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477690</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478008</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>CV; Cover Letter; Job Market Paper</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -5903,7 +5982,12 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477690</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478008</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>banking@nccu.edu.tw</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -5920,22 +6004,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Taoyuan City</t>
+          <t>Taipei</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>National Central University</t>
+          <t>National Chengchi University</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Department of Finance</t>
+          <t>The Department of International Business</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
-        <v>46402</v>
+        <v>46458</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -5944,12 +6028,12 @@
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477637</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478133</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Job Market Paper</t>
+          <t>CV; Cover Letter; Job Market Paper</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -5959,12 +6043,7 @@
       </c>
       <c r="K108" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477637</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>ncu6250@ncu.edu.tw</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478133</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -5981,22 +6060,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Tainan</t>
+          <t>Minhsiung, CHIAYI</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>National Cheng Kung University</t>
+          <t>National Chung Cheng University</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Economics</t>
+          <t>Department of Economics</t>
         </is>
       </c>
       <c r="F109" s="2" t="n">
-        <v>46354</v>
+        <v>46418</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -6005,12 +6084,12 @@
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477925</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477555</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Cover Letter</t>
+          <t>Cover Letter; Research Papers; Research Statement; Transcript</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6020,7 +6099,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477925</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477555</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -6037,22 +6116,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Taipei</t>
+          <t>Kaohsiung</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>National Chengchi University</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>National Sun Yat-sen University</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>985/211</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Department of Economics</t>
+          <t>Department of Political Economy</t>
         </is>
       </c>
       <c r="F110" s="2" t="n">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -6061,7 +6144,12 @@
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477745</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477532</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Cover Letter; Job Market Paper; Teaching Statement; Research Statement</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6071,12 +6159,12 @@
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477745</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477532</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>econ@nccu.edu.tw</t>
+          <t>poleco@mail.nsysu.edu.tw</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -6093,22 +6181,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Taipei</t>
+          <t>New Taipei City</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>National Chengchi University</t>
+          <t>National Taipei University</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>College of Global Banking and Finance</t>
+          <t>Department of Economics</t>
         </is>
       </c>
       <c r="F111" s="2" t="n">
-        <v>46387</v>
+        <v>46366</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -6117,12 +6205,7 @@
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477791 | https://cgbf.nccu.edu.tw/</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>CV; Job Market Paper</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477648</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6132,12 +6215,12 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>https://cgbf.nccu.edu.tw/</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477648</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>pthung@mail3.nccu.tw</t>
+          <t>econ_job@mail.ntpu.edu.tw; tapply@gm.ntpu.edu.tw</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -6159,13 +6242,13 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>National Chengchi University</t>
+          <t>National Taiwan University</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Department of Money and Banking</t>
+          <t>Department of Economics</t>
         </is>
       </c>
       <c r="F112" s="2" t="n">
@@ -6178,12 +6261,7 @@
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478008</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>CV; Cover Letter; Job Market Paper</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477929 | https://econ.ntu.edu.tw</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6193,12 +6271,12 @@
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478008</t>
+          <t>https://econ.ntu.edu.tw</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>banking@nccu.edu.tw</t>
+          <t>kuanmingchen@ntu.edu.tw</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -6215,22 +6293,26 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Taipei</t>
+          <t>Hsinchu</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>National Chengchi University</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
+          <t>National Tsing Hua University</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>985/211</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>The Department of International Business</t>
+          <t>Taipei School of Economics and Political Science (TSE)</t>
         </is>
       </c>
       <c r="F113" s="2" t="n">
-        <v>46458</v>
+        <v>46341</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -6239,12 +6321,7 @@
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478133</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>CV; Cover Letter; Job Market Paper</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477721 | https://www.tse.nthu.edu.tw/</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -6254,7 +6331,12 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478133</t>
+          <t>https://www.tse.nthu.edu.tw/</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>tse@my.nthu.edu.tw</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -6271,22 +6353,26 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Minhsiung, CHIAYI</t>
+          <t>Hsinchu City, Hsinchu</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>National Chung Cheng University</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
+          <t>National Tsing Hua University</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>985/211</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Department of Economics</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F114" s="2" t="n">
-        <v>46418</v>
+        <v>46355</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -6295,12 +6381,7 @@
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477555</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>Cover Letter; Research Papers; Research Statement; Transcript</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477989</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -6310,302 +6391,10 @@
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477555</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477989</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>TAIWAN</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Kaohsiung</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>National Sun Yat-sen University</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Department of Political Economy</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="n">
-        <v>46387</v>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H115" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477532</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>Cover Letter; Job Market Paper; Teaching Statement; Research Statement</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>AEA</t>
-        </is>
-      </c>
-      <c r="K115" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477532</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>poleco@mail.nsysu.edu.tw</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>TAIWAN</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>New Taipei City</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>National Taipei University</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Department of Economics</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="n">
-        <v>46366</v>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H116" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477648</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>AEA</t>
-        </is>
-      </c>
-      <c r="K116" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477648</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>econ_job@mail.ntpu.edu.tw; tapply@gm.ntpu.edu.tw</t>
-        </is>
-      </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>TAIWAN</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Taipei</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>National Taiwan University</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Department of Economics</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="n">
-        <v>46418</v>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H117" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477929 | https://econ.ntu.edu.tw</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>AEA</t>
-        </is>
-      </c>
-      <c r="K117" s="3" t="inlineStr">
-        <is>
-          <t>https://econ.ntu.edu.tw</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>kuanmingchen@ntu.edu.tw</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>TAIWAN</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Hsinchu</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>National Tsing Hua University</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Taipei School of Economics and Political Science (TSE)</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="n">
-        <v>46341</v>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477721 | https://www.tse.nthu.edu.tw/</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>AEA</t>
-        </is>
-      </c>
-      <c r="K118" s="3" t="inlineStr">
-        <is>
-          <t>https://www.tse.nthu.edu.tw/</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>tse@my.nthu.edu.tw</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>TAIWAN</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Hsinchu City, Hsinchu</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>National Tsing Hua University</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Economics</t>
-        </is>
-      </c>
-      <c r="F119" s="2" t="n">
-        <v>46355</v>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H119" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477989</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>AEA</t>
-        </is>
-      </c>
-      <c r="K119" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477989</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
@@ -6839,16 +6628,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId224"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId225"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K114" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K116" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K117" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K118" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId236"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/clean/aea_listings_2026-10-15.xlsx
+++ b/clean/aea_listings_2026-10-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M114"/>
+  <dimension ref="A1:M113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>46418</v>
+        <v>46357</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>46402</v>
+        <v>46366</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -3309,19 +3309,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Capital University of Economics and Business</t>
+          <t>Dongbei University of Finance &amp; Economics</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>International School of Economics and Management</t>
+          <t>Dongbei University Of Finance And Economics</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=230A8F8CAE8FB702</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=9058523321C2911A</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=230A8F8CAE8FB702</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=9058523321C2911A</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3348,19 +3348,23 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dongbei University of Finance &amp; Economics</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>Donghua University</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dongbei University Of Finance And Economics</t>
+          <t>Glorious Sun School of Business and Management</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=9058523321C2911A</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=1CE68DDB85B84365</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3370,7 +3374,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=9058523321C2911A</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=1CE68DDB85B84365</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3387,23 +3391,26 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Donghua University</t>
+          <t>Fudan University</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>985/211</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Glorious Sun School of Business and Management</t>
-        </is>
+          <t>School of Economics</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>46327</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=1CE68DDB85B84365</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=E968D280DD59D564</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3413,7 +3420,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=1CE68DDB85B84365</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=E968D280DD59D564</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3440,16 +3447,18 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>School of Economics</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="n">
-        <v>46327</v>
+          <t>School of Management</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=E968D280DD59D564</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=E153FEE8CC8E11B5</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3459,12 +3468,12 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=E968D280DD59D564</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=E153FEE8CC8E11B5</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -3476,28 +3485,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Fudan University</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
+          <t>Harbin Institute of Technology</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>School of Management</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Rolling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=E153FEE8CC8E11B5</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3ED8A58471D2F80B</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=E153FEE8CC8E11B5</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3ED8A58471D2F80B</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3524,19 +3524,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Harbin Institute of Technology</t>
+          <t>Huazhong University of Science and Technology</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>School of Management</t>
+          <t>School of Economics, Huazhong University of Science &amp; Technology</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3ED8A58471D2F80B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A380FA8882023C78</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>CV; Job Market Paper; Letters of Reference</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3546,12 +3551,12 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3ED8A58471D2F80B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A380FA8882023C78</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -3563,24 +3568,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Huazhong University of Science and Technology</t>
+          <t>Hunan University</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>School of Economics, Huazhong University of Science &amp; Technology</t>
+          <t>School of Economics and Trade</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A380FA8882023C78</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>CV; Job Market Paper; Letters of Reference</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=38CE3CA2770AB83B</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A380FA8882023C78</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=38CE3CA2770AB83B</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -3607,19 +3607,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hunan University</t>
+          <t>Lanzhou University of Finance and Economics</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>School of Economics and Trade</t>
+          <t>the Office of Personnel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=38CE3CA2770AB83B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=003923B6EFE42FFF</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=38CE3CA2770AB83B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=003923B6EFE42FFF</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -3646,19 +3646,23 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jilin University</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>Nanjing Agricultural University</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>985/211</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Business School</t>
+          <t>College of Finance</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A4E054BFC7078E2F</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=41CE1E8D1AE20F34</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3668,7 +3672,7 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A4E054BFC7078E2F</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=41CE1E8D1AE20F34</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -3685,19 +3689,23 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lanzhou University of Finance and Economics</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>Nanjing University</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>985/211</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>the Office of Personnel</t>
+          <t>Business School</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=003923B6EFE42FFF</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=5EE87D5DE6734D4D</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3707,7 +3715,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=003923B6EFE42FFF</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=5EE87D5DE6734D4D</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -3724,7 +3732,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Nanjing Agricultural University</t>
+          <t>Peking University</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3734,13 +3742,16 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>College of Finance</t>
-        </is>
+          <t>Peking University HSBC Business School</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>46364</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=41CE1E8D1AE20F34</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3750,7 +3761,7 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=41CE1E8D1AE20F34</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -3767,7 +3778,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Nanjing University</t>
+          <t>Peking University</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3777,13 +3788,18 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Business School</t>
+          <t>Guanghua School of Management</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=5EE87D5DE6734D4D</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3793,7 +3809,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=5EE87D5DE6734D4D</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -3810,7 +3826,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Nankai University</t>
+          <t>Renmin University of China</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3820,13 +3836,16 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>School of Finance</t>
-        </is>
+          <t>School of Finance, Renmin University of China</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>46357</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=96728BEC2B0A48B6</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3836,7 +3855,7 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=96728BEC2B0A48B6</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -3853,26 +3872,28 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Peking University</t>
+          <t>Shanghai Institute for Mathematics and Interdisciplinary Sciences</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>985/211</t>
+          <t>211</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Peking University HSBC Business School</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="n">
-        <v>46364</v>
+          <t>The Shanghai Institute for Mathematics and Interdisciplinary Sciences</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=D6296C379B46AFF9</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3882,7 +3903,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=D6296C379B46AFF9</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -3899,28 +3920,26 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Peking University</t>
+          <t>Shanghai Jiao Tong University</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>985/211</t>
+          <t>211</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Guanghua School of Management</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Rolling</t>
-        </is>
+          <t>Antai College of Economics and Management</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>46341</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3930,7 +3949,7 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -3947,26 +3966,23 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Renmin University of China</t>
+          <t>Shanghai University of Finance and Economics</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>985/211</t>
+          <t>211</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>School of Finance, Renmin University of China</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="n">
-        <v>46357</v>
+          <t>School of Economics</t>
+        </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3976,7 +3992,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -3993,26 +4009,28 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Shanghai Jiao Tong University</t>
+          <t>Sun Yat-sen University</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>985/211</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Antai College of Economics and Management</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="n">
-        <v>46341</v>
+          <t>Lingnan College</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=73CF283104D9C7BB</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4022,12 +4040,12 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=73CF283104D9C7BB</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -4039,23 +4057,26 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Shanghai University of Finance Economics School</t>
+          <t>Tsinghua University</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>985/211</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>School of Digital Economy</t>
-        </is>
+          <t>School of Economics and Management</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>46356</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=7E509CEAE1E65959</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4065,7 +4086,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=7E509CEAE1E65959</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -4082,23 +4103,23 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Shanghai University of Finance and Economics</t>
+          <t>Tsinghua University</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>985/211</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>School of Economics</t>
+          <t>Center for International Finance and Economics Research</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4108,12 +4129,12 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -4125,19 +4146,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Southwestern University of Finance and Economics</t>
+          <t>University of Electronic Science and Technology of China</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>School of Economics</t>
+          <t>School of Management and Economics</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=8F2A4E7B41A62BEC</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4147,12 +4168,12 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=8F2A4E7B41A62BEC</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -4164,26 +4185,19 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tsinghua University</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
+          <t>University of Science and Technology of China</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>School of Economics and Management</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="n">
-        <v>46356</v>
+          <t>Institute of International Finance</t>
+        </is>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4193,12 +4207,12 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -4210,23 +4224,19 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tsinghua University</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
+          <t>University of Science and Technology of China</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Center for International Finance and Economics Research</t>
+          <t>School of Management</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4236,7 +4246,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -4253,19 +4263,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>University of Electronic Science and Technology of China</t>
+          <t>Xi%u2019an Jiaotong University</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>School of Management and Economics</t>
+          <t>School of Economics and Finance</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4275,7 +4285,7 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -4292,19 +4302,19 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>University of Science and Technology of China</t>
+          <t>Xi%u2019an Jiaotong-Liverpool University</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Institute of International Finance</t>
+          <t>International Business School Suzhou (IBSS), Department of Economics</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4314,7 +4324,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -4331,19 +4341,28 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>University of Science and Technology of China</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t>Zhejiang University</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>985/211</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>School of Management</t>
+          <t>School of Economics</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=7D928B7B1C35099A</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4353,7 +4372,7 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=7D928B7B1C35099A</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -4370,19 +4389,23 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Xi%u2019an Jiaotong University</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t>Zhejiang University</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>985/211</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>School of Economics and Finance</t>
+          <t>International Business School</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4392,12 +4415,12 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -4409,19 +4432,19 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Xi%u2019an Jiaotong-Liverpool University</t>
+          <t>Zhongnan Unviersity of Economics and Law</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>International Business School Suzhou (IBSS), Department of Economics</t>
+          <t>School of Finance</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4431,7 +4454,7 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -4443,38 +4466,52 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Kowloon Tong, Kowloon</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Zhejiang University</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
+          <t>City University of Hong Kong</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>International Business School</t>
-        </is>
+          <t>Economics and Finance</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>46356</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
+          <t>https://econjobmarket.org/positions/12596</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Job Market Paper; Research Statement</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>CICE</t>
+          <t>EJM</t>
         </is>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
+          <t>https://econjobmarket.org/positions/12596</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>efpost@cityu.edu.hk</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -4486,34 +4523,47 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Pokfulam Road</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Zhongnan Unviersity of Economics and Law</t>
+          <t>University of Hong Kong</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>School of Finance</t>
-        </is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>46341</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
+          <t>https://econjobmarket.org/positions/12521</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>CICE</t>
+          <t>EJM</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
+          <t>https://econjobmarket.org/positions/12521</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>orgecon@hku.hk</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -4530,18 +4580,18 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Kowloon Tong, Kowloon</t>
+          <t>Pokfulam Road</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>City University of Hong Kong</t>
+          <t>University of Hong Kong</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Economics and Finance</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
@@ -4550,12 +4600,12 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12596</t>
+          <t>https://econjobmarket.org/positions/12581</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Job Market Paper; Research Statement</t>
+          <t>Job Market Paper</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4565,12 +4615,12 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12596</t>
+          <t>https://econjobmarket.org/positions/12581</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>efpost@cityu.edu.hk</t>
+          <t>econ.jobmarket@hku.hk</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -4582,47 +4632,51 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Pokfulam Road</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>University of Hong Kong</t>
+          <t>City University of Hong Kong</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Economics</t>
+          <t>Department of Economics and Finance</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
-        <v>46341</v>
-      </c>
-      <c r="G82" t="inlineStr"/>
+        <v>46356</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12521</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477722 | http://jobs.cityu.edu.hk</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Job Market Paper; Research Statement</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>EJM</t>
+          <t>AEA</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12521</t>
+          <t>http://jobs.cityu.edu.hk</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>orgecon@hku.hk</t>
+          <t>efpost@cityu.edu.hk</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -4634,52 +4688,51 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Pokfulam Road</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>University of Hong Kong</t>
+          <t>City University of Hong Kong</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Economics</t>
+          <t>Department of Economics and Finance</t>
         </is>
       </c>
       <c r="F83" s="2" t="n">
         <v>46356</v>
       </c>
-      <c r="G83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12581</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477723 | http://jobs.cityu.edu.hk</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Job Market Paper</t>
+          <t>Job Market Paper; Research Statement</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>EJM</t>
+          <t>AEA</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12581</t>
+          <t>http://jobs.cityu.edu.hk</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>econ.jobmarket@hku.hk</t>
+          <t>efpost@cityu.edu.hk</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -4700,13 +4753,8 @@
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Department of Economics and Finance</t>
-        </is>
-      </c>
       <c r="F84" s="2" t="n">
-        <v>46356</v>
+        <v>46418</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4715,12 +4763,7 @@
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477722 | http://jobs.cityu.edu.hk</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Job Market Paper; Research Statement</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477624 | https://www.cityu.edu.hk/academic/colleges-schools-and-departments</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4730,12 +4773,7 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>http://jobs.cityu.edu.hk</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>efpost@cityu.edu.hk</t>
+          <t>https://www.cityu.edu.hk/academic/colleges-schools-and-departments</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -4750,19 +4788,24 @@
           <t>HONG KONG</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Hong Kong, Hong Kong</t>
+        </is>
+      </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>City University of Hong Kong</t>
+          <t>Hong Kong University of Science and Technology</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Department of Economics and Finance</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>46356</v>
+        <v>46348</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4771,12 +4814,12 @@
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477723 | http://jobs.cityu.edu.hk</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477656 | https://apply.interfolio.com/191029</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Job Market Paper; Research Statement</t>
+          <t>Research Papers</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4786,12 +4829,12 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>http://jobs.cityu.edu.hk</t>
+          <t>https://apply.interfolio.com/191029</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>efpost@cityu.edu.hk</t>
+          <t>econjob@ust.hk</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -4808,12 +4851,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>City University of Hong Kong</t>
+          <t>The Chinese University of Hong Kong</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Department of Decisions, Operations and Technology</t>
+        </is>
+      </c>
       <c r="F86" s="2" t="n">
-        <v>46418</v>
+        <v>46387</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4822,7 +4870,12 @@
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477624 | https://www.cityu.edu.hk/academic/colleges-schools-and-departments</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477636 | http://career.cuhk.edu.hk</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Teaching Evaluations</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -4832,7 +4885,12 @@
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>https://www.cityu.edu.hk/academic/colleges-schools-and-departments</t>
+          <t>http://career.cuhk.edu.hk</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>dote@cuhk.edu.hk</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -4847,14 +4905,9 @@
           <t>HONG KONG</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Hong Kong, Hong Kong</t>
-        </is>
-      </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Hong Kong University of Science and Technology</t>
+          <t>The University of Hong Kong</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -4864,7 +4917,7 @@
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>46348</v>
+        <v>46336</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4873,12 +4926,12 @@
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477656 | https://apply.interfolio.com/191029</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477668 | https://jobs.hku.hk</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Research Papers</t>
+          <t>Job Market Paper</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -4888,12 +4941,12 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>https://apply.interfolio.com/191029</t>
+          <t>https://jobs.hku.hk</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>econjob@ust.hk</t>
+          <t>econ.jobmarket@hku.hk</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -4905,22 +4958,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>JAPAN</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Tokyo, Tokyo</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>The Chinese University of Hong Kong</t>
+          <t>Bank of Japan</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Department of Decisions, Operations and Technology</t>
+          <t>Institute for Monetary and Economic Studies (IMES)</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
-        <v>46387</v>
+        <v>46356</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4929,12 +4987,12 @@
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477636 | http://career.cuhk.edu.hk</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477873</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Teaching Evaluations</t>
+          <t>Research Papers</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -4944,12 +5002,7 @@
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>http://career.cuhk.edu.hk</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>dote@cuhk.edu.hk</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477873</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -4961,22 +5014,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>JAPAN</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Minato-Ku, Tokyo</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>The University of Hong Kong</t>
+          <t>Japan Fair Trade Commission</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Economics</t>
-        </is>
-      </c>
       <c r="F89" s="2" t="n">
-        <v>46356</v>
+        <v>46418</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -4985,12 +5038,12 @@
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477668 | https://jobs.hku.hk</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477599 | https://www.jftc.go.jp/soshiki/recruit/specialty.html</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Job Market Paper</t>
+          <t>Research Papers</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5000,12 +5053,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.hku.hk</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>econ.jobmarket@hku.hk</t>
+          <t>https://www.jftc.go.jp/soshiki/recruit/specialty.html</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -5027,17 +5075,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bank of Japan</t>
+          <t>Musashi University</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Institute for Monetary and Economic Studies (IMES)</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>46356</v>
+        <v>46326</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -5046,12 +5094,7 @@
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477873</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>Research Papers</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477561 | https://jrecin.jst.go.jp/seek/SeekJorDetail/Changelang?id=D126070158&amp;lang=1</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5061,7 +5104,7 @@
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477873</t>
+          <t>https://jrecin.jst.go.jp/seek/SeekJorDetail/Changelang?id=D126070158&amp;lang=1</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -5078,17 +5121,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Minato-Ku, Tokyo</t>
+          <t>Yushima, Bunkyo, Tokyo</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Japan Fair Trade Commission</t>
+          <t>UTokyo Economic Consulting Inc.</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="F91" s="2" t="n">
-        <v>46418</v>
+        <v>46356</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -5097,12 +5140,7 @@
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477599 | https://www.jftc.go.jp/soshiki/recruit/specialty.html</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Research Papers</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477714 | https://utecon.net/en/</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5112,7 +5150,12 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>https://www.jftc.go.jp/soshiki/recruit/specialty.html</t>
+          <t>https://utecon.net/en/</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>recruit@utecon.net</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -5129,22 +5172,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tokyo, Tokyo</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Musashi University</t>
+          <t>Waseda University</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Economics</t>
-        </is>
-      </c>
       <c r="F92" s="2" t="n">
-        <v>46326</v>
+        <v>46310</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -5153,7 +5191,7 @@
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477561 | https://jrecin.jst.go.jp/seek/SeekJorDetail/Changelang?id=D126070158&amp;lang=1</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477611 | https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26944/</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5163,7 +5201,7 @@
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>https://jrecin.jst.go.jp/seek/SeekJorDetail/Changelang?id=D126070158&amp;lang=1</t>
+          <t>https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26944/</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -5180,17 +5218,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Yushima, Bunkyo, Tokyo</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>UTokyo Economic Consulting Inc.</t>
+          <t>Waseda University</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Faculty of Political Science and Economics (FPSE)</t>
+        </is>
+      </c>
       <c r="F93" s="2" t="n">
-        <v>46356</v>
+        <v>46310</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -5199,7 +5242,7 @@
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477714 | https://utecon.net/en/</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477612 | https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26955/</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5209,12 +5252,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>https://utecon.net/en/</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>recruit@utecon.net</t>
+          <t>https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26955/</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -5226,41 +5264,52 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>JAPAN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Kyoto, Kyoto</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Waseda University</t>
+          <t>Kyoto University</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Institute for Economic Research</t>
+        </is>
+      </c>
       <c r="F94" s="2" t="n">
-        <v>46310</v>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+        <v>46332</v>
+      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477611 | https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26944/</t>
+          <t>https://econjobmarket.org/positions/12683</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Research Papers</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>AEA</t>
+          <t>EJM</t>
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26944/</t>
+          <t>https://econjobmarket.org/positions/12683</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>soumu-jinji@kier.kyoto-u.ac.jp</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -5272,27 +5321,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>JAPAN</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Tokyo</t>
+          <t>MACAO; CHINA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Waseda University</t>
+          <t>University of Macau (UM)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Faculty of Political Science and Economics (FPSE)</t>
+          <t>Department of Finance and Business Economics</t>
         </is>
       </c>
       <c r="F95" s="2" t="n">
-        <v>46310</v>
+        <v>46356</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -5301,7 +5345,12 @@
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477612 | https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26955/</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477678 | https://career.admo.um.edu.mo/learn-more</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>CV; Cover Letter; Job Market Paper; Research Papers; Teaching Evaluations; Letters of Reference</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5311,7 +5360,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26955/</t>
+          <t>https://career.admo.um.edu.mo/learn-more</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -5323,52 +5372,50 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>MALAYSIA</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Kyoto, Kyoto</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Kyoto University</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Institute for Economic Research</t>
+          <t>The South East Asian Central Banks (SEACEN) Research and Training Centre</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>985/211</t>
         </is>
       </c>
       <c r="F96" s="2" t="n">
-        <v>46332</v>
-      </c>
-      <c r="G96" t="inlineStr"/>
+        <v>46418</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12683</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>Research Papers</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477702 | https://www.seacen.org/</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>EJM</t>
+          <t>AEA</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12683</t>
+          <t>https://www.seacen.org/</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>soumu-jinji@kier.kyoto-u.ac.jp</t>
+          <t>hr@seacen.org</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -5380,43 +5427,47 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MACAO; CHINA</t>
+          <t>MY</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur, Malaysia</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>University of Macau (UM)</t>
+          <t>Asia School of Business</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Department of Finance and Business Economics</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+          <t>All departments</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>46356</v>
+      </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477678 | https://career.admo.um.edu.mo/learn-more</t>
+          <t>https://econjobmarket.org/positions/12494</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>CV; Cover Letter; Job Market Paper; Research Papers; Teaching Evaluations; Letters of Reference</t>
+          <t>CV; Teaching Statement</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>AEA</t>
+          <t>EJM</t>
         </is>
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>https://career.admo.um.edu.mo/learn-more</t>
+          <t>https://econjobmarket.org/positions/12494</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -5428,47 +5479,51 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>NEW ZEALAND</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Kuala Lumpur, Malaysia</t>
+          <t>Auckland, Auckland</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Asia School of Business</t>
+          <t>The University of Auckland</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>All departments</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F98" s="2" t="n">
-        <v>46356</v>
-      </c>
-      <c r="G98" t="inlineStr"/>
+        <v>46321</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12494</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478084 | https://jobs.smartrecruiters.com/TheUniversityOfAuckland/744000151521321-lecturer-senior-lecturer-economics</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>CV; Teaching Statement</t>
+          <t>CV; Cover Letter; Teaching Evaluations</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>EJM</t>
+          <t>AEA</t>
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12494</t>
+          <t>https://jobs.smartrecruiters.com/TheUniversityOfAuckland/744000151521321-lecturer-senior-lecturer-economics</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -5480,27 +5535,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>NEW ZEALAND</t>
+          <t>TAIWAN</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Auckland, Auckland</t>
+          <t>Taipei</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>The University of Auckland</t>
+          <t>Institute of Economics, Academia Sinica (IEAS)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Economics</t>
-        </is>
-      </c>
       <c r="F99" s="2" t="n">
-        <v>46321</v>
+        <v>46357</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -5509,12 +5559,12 @@
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478084 | https://jobs.smartrecruiters.com/TheUniversityOfAuckland/744000151521321-lecturer-senior-lecturer-economics</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477843 | https://www.econ.sinica.edu.tw/</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>CV; Cover Letter; Teaching Evaluations</t>
+          <t>Cover Letter; Job Market Paper</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5524,7 +5574,12 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/TheUniversityOfAuckland/744000151521321-lecturer-senior-lecturer-economics</t>
+          <t>https://www.econ.sinica.edu.tw/</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>searchcommit@econ.sinica.edu.tw</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -5541,17 +5596,22 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Taipei</t>
+          <t>Taoyuan</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Institute of Economics, Academia Sinica (IEAS)</t>
+          <t>National Central University</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
       <c r="F100" s="2" t="n">
-        <v>46357</v>
+        <v>46358</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -5560,12 +5620,12 @@
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477843 | https://www.econ.sinica.edu.tw/</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477598</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Cover Letter; Job Market Paper</t>
+          <t>CV; Cover Letter; Job Market Paper; Transcript</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5575,12 +5635,12 @@
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>https://www.econ.sinica.edu.tw/</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477598</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>searchcommit@econ.sinica.edu.tw</t>
+          <t>ncu66301@ncu.edu.tw</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -5597,7 +5657,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Taoyuan</t>
+          <t>Zhongli, Taoyuan</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5608,11 +5668,11 @@
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Economics</t>
+          <t>Graduate Institute of Industrial Economics</t>
         </is>
       </c>
       <c r="F101" s="2" t="n">
-        <v>46358</v>
+        <v>46368</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -5621,12 +5681,7 @@
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477598</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>CV; Cover Letter; Job Market Paper; Transcript</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477690</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -5636,12 +5691,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477598</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>ncu66301@ncu.edu.tw</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477690</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -5658,7 +5708,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Zhongli, Taoyuan</t>
+          <t>Taoyuan City</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5669,11 +5719,11 @@
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Graduate Institute of Industrial Economics</t>
+          <t>Department of Finance</t>
         </is>
       </c>
       <c r="F102" s="2" t="n">
-        <v>46368</v>
+        <v>46402</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -5682,7 +5732,12 @@
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477690</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477637</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Job Market Paper</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -5692,7 +5747,12 @@
       </c>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477690</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477637</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>ncu6250@ncu.edu.tw</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -5709,22 +5769,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Taoyuan City</t>
+          <t>Tainan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>National Central University</t>
+          <t>National Cheng Kung University</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Department of Finance</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F103" s="2" t="n">
-        <v>46402</v>
+        <v>46354</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -5733,12 +5793,12 @@
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477637</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477925</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Job Market Paper</t>
+          <t>Cover Letter</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -5748,12 +5808,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477637</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>ncu6250@ncu.edu.tw</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477925</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -5770,22 +5825,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Tainan</t>
+          <t>Taipei</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>National Cheng Kung University</t>
+          <t>National Chengchi University</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Economics</t>
+          <t>Department of Economics</t>
         </is>
       </c>
       <c r="F104" s="2" t="n">
-        <v>46354</v>
+        <v>46356</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -5794,12 +5849,7 @@
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477925</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>Cover Letter</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477745</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -5809,7 +5859,12 @@
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477925</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477745</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>econ@nccu.edu.tw</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -5837,11 +5892,11 @@
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Department of Economics</t>
+          <t>College of Global Banking and Finance</t>
         </is>
       </c>
       <c r="F105" s="2" t="n">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -5850,7 +5905,12 @@
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477745</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477791 | https://cgbf.nccu.edu.tw/</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>CV; Job Market Paper</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -5860,12 +5920,12 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477745</t>
+          <t>https://cgbf.nccu.edu.tw/</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>econ@nccu.edu.tw</t>
+          <t>pthung@mail3.nccu.tw</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -5893,11 +5953,11 @@
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>College of Global Banking and Finance</t>
+          <t>Department of Money and Banking</t>
         </is>
       </c>
       <c r="F106" s="2" t="n">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -5906,12 +5966,12 @@
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477791 | https://cgbf.nccu.edu.tw/</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478008</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>CV; Job Market Paper</t>
+          <t>CV; Cover Letter; Job Market Paper</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -5921,12 +5981,12 @@
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>https://cgbf.nccu.edu.tw/</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478008</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>pthung@mail3.nccu.tw</t>
+          <t>banking@nccu.edu.tw</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -5954,11 +6014,11 @@
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Department of Money and Banking</t>
+          <t>The Department of International Business</t>
         </is>
       </c>
       <c r="F107" s="2" t="n">
-        <v>46418</v>
+        <v>46458</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -5967,7 +6027,7 @@
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478008</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478133</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5982,12 +6042,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478008</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>banking@nccu.edu.tw</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478133</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -6004,22 +6059,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Taipei</t>
+          <t>Minhsiung, CHIAYI</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>National Chengchi University</t>
+          <t>National Chung Cheng University</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>The Department of International Business</t>
+          <t>Department of Economics</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
-        <v>46458</v>
+        <v>46418</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -6028,12 +6083,12 @@
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478133</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477555</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>CV; Cover Letter; Job Market Paper</t>
+          <t>Cover Letter; Research Papers; Research Statement; Transcript</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -6043,7 +6098,7 @@
       </c>
       <c r="K108" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478133</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477555</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -6060,22 +6115,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Minhsiung, CHIAYI</t>
+          <t>Kaohsiung</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>National Chung Cheng University</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>National Sun Yat-sen University</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>985/211</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Department of Economics</t>
+          <t>Department of Political Economy</t>
         </is>
       </c>
       <c r="F109" s="2" t="n">
-        <v>46418</v>
+        <v>46387</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -6084,12 +6143,12 @@
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477555</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477532</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Cover Letter; Research Papers; Research Statement; Transcript</t>
+          <t>Cover Letter; Job Market Paper; Teaching Statement; Research Statement</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6099,7 +6158,12 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477555</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477532</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>poleco@mail.nsysu.edu.tw</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -6116,26 +6180,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Kaohsiung</t>
+          <t>New Taipei City</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>National Sun Yat-sen University</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
+          <t>National Taipei University</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Department of Political Economy</t>
+          <t>Department of Economics</t>
         </is>
       </c>
       <c r="F110" s="2" t="n">
-        <v>46387</v>
+        <v>46366</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -6144,12 +6204,7 @@
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477532</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>Cover Letter; Job Market Paper; Teaching Statement; Research Statement</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477648</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6159,12 +6214,12 @@
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477532</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477648</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>poleco@mail.nsysu.edu.tw</t>
+          <t>econ_job@mail.ntpu.edu.tw; tapply@gm.ntpu.edu.tw</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -6181,12 +6236,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>New Taipei City</t>
+          <t>Taipei</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>National Taipei University</t>
+          <t>National Taiwan University</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -6196,7 +6251,7 @@
         </is>
       </c>
       <c r="F111" s="2" t="n">
-        <v>46366</v>
+        <v>46418</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -6205,7 +6260,7 @@
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477648</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477929 | https://econ.ntu.edu.tw</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6215,12 +6270,12 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477648</t>
+          <t>https://econ.ntu.edu.tw</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>econ_job@mail.ntpu.edu.tw; tapply@gm.ntpu.edu.tw</t>
+          <t>kuanmingchen@ntu.edu.tw</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -6237,22 +6292,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Taipei</t>
+          <t>Hsinchu</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>National Taiwan University</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
+          <t>National Tsing Hua University</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>985/211</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Department of Economics</t>
+          <t>Taipei School of Economics and Political Science (TSE)</t>
         </is>
       </c>
       <c r="F112" s="2" t="n">
-        <v>46418</v>
+        <v>46341</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -6261,7 +6320,7 @@
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477929 | https://econ.ntu.edu.tw</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477721 | https://www.tse.nthu.edu.tw/</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6271,12 +6330,12 @@
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>https://econ.ntu.edu.tw</t>
+          <t>https://www.tse.nthu.edu.tw/</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>kuanmingchen@ntu.edu.tw</t>
+          <t>tse@my.nthu.edu.tw</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -6293,7 +6352,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Hsinchu</t>
+          <t>Hsinchu City, Hsinchu</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6308,11 +6367,11 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Taipei School of Economics and Political Science (TSE)</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F113" s="2" t="n">
-        <v>46341</v>
+        <v>46355</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -6321,7 +6380,7 @@
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477721 | https://www.tse.nthu.edu.tw/</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477989</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -6331,70 +6390,10 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>https://www.tse.nthu.edu.tw/</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>tse@my.nthu.edu.tw</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477989</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>TAIWAN</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Hsinchu City, Hsinchu</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>National Tsing Hua University</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Economics</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="n">
-        <v>46355</v>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H114" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477989</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>AEA</t>
-        </is>
-      </c>
-      <c r="K114" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477989</t>
-        </is>
-      </c>
-      <c r="M114" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
@@ -6626,8 +6625,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId222"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId223"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K114" r:id="rId226"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/clean/aea_listings_2026-10-15.xlsx
+++ b/clean/aea_listings_2026-10-15.xlsx
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -55,10 +53,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -425,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M113"/>
+  <dimension ref="A1:M111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -526,19 +523,19 @@
           <t>Australian National University</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Research School of Economics</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
-        <v>46361</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>https://econjobmarket.org/positions/12610</t>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-12-05</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -546,7 +543,7 @@
           <t>EJM</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12610</t>
         </is>
@@ -578,19 +575,19 @@
           <t>Monash University</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Department of Economics</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n">
-        <v>46326</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>https://econjobmarket.org/positions/12472</t>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -603,7 +600,7 @@
           <t>EJM</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12472</t>
         </is>
@@ -635,19 +632,19 @@
           <t>Reserve Bank of Australia</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>All departments</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n">
-        <v>46357</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>https://econjobmarket.org/positions/12722</t>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -660,7 +657,7 @@
           <t>EJM</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12722</t>
         </is>
@@ -692,19 +689,19 @@
           <t>University of Melbourne</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Department of Economics</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n">
-        <v>46351</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>https://econjobmarket.org/positions/12779</t>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -717,7 +714,7 @@
           <t>EJM</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12779</t>
         </is>
@@ -749,19 +746,19 @@
           <t>University of New South Wales (UNSW), Sydney</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>School of Economics, Business School</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
-        <v>46353</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>https://econjobmarket.org/positions/12744</t>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -774,7 +771,7 @@
           <t>EJM</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12744</t>
         </is>
@@ -806,19 +803,19 @@
           <t>University of New South Wales (UNSW), Sydney</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>School of Banking and Finance</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n">
-        <v>46418</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>https://econjobmarket.org/positions/12681</t>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -831,7 +828,7 @@
           <t>EJM</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12681</t>
         </is>
@@ -863,19 +860,19 @@
           <t>University of Queensland</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>School of Economics</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n">
-        <v>46327</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>https://econjobmarket.org/positions/12721</t>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -888,7 +885,7 @@
           <t>EJM</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12721</t>
         </is>
@@ -920,23 +917,24 @@
           <t>Australian National University</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Research School of Economics</t>
         </is>
       </c>
-      <c r="F9" s="2" t="n">
-        <v>46361</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-12-05</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477886 | https://econjobmarket.org/positions/12610</t>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -944,7 +942,7 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12610</t>
         </is>
@@ -976,23 +974,24 @@
           <t>Reserve Bank of Australia</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Economic Research Department</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n">
-        <v>46357</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478037 | https://www.rba.gov.au/careers/careers-at-the-rba/economic-and-finance.html</t>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1000,7 +999,7 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>https://www.rba.gov.au/careers/careers-at-the-rba/economic-and-finance.html</t>
         </is>
@@ -1032,23 +1031,24 @@
           <t>The University of Queensland</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>School of Economics</t>
         </is>
       </c>
-      <c r="F11" s="2" t="n">
-        <v>46327</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478036</t>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1056,7 +1056,7 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478036</t>
         </is>
@@ -1088,18 +1088,19 @@
           <t>UNSW Sydney</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="F12" s="2" t="n">
-        <v>46353</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478270</t>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1107,7 +1108,7 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478270</t>
         </is>
@@ -1134,23 +1135,24 @@
           <t>China Europe International Business School</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Economics and Decision Sciences</t>
         </is>
       </c>
-      <c r="F13" s="2" t="n">
-        <v>46357</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477872</t>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1163,7 +1165,7 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477872</t>
         </is>
@@ -1195,23 +1197,24 @@
           <t>East China University of Science and Technology</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Department of Economics</t>
         </is>
       </c>
-      <c r="F14" s="2" t="n">
-        <v>46418</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478052 | http://bs.ecust.edu.cn/</t>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1219,7 +1222,7 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>http://bs.ecust.edu.cn/</t>
         </is>
@@ -1261,17 +1264,19 @@
           <t>School of Economics</t>
         </is>
       </c>
-      <c r="F15" s="2" t="n">
-        <v>46327</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477852 | https://econ.fudan.edu.cn/</t>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1284,7 +1289,7 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>https://econ.fudan.edu.cn/</t>
         </is>
@@ -1316,18 +1321,19 @@
           <t>Hong Kong Monetary Authority</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="F16" s="2" t="n">
-        <v>46326</v>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478035 | http://www.hkma.gov.hk</t>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1335,7 +1341,7 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>http://www.hkma.gov.hk</t>
         </is>
@@ -1362,23 +1368,24 @@
           <t>Huazhong University of Science and Technology</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>School of Economics</t>
         </is>
       </c>
-      <c r="F17" s="2" t="n">
-        <v>46356</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478111 | http://eco.hust.edu.cn</t>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1386,7 +1393,7 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>http://eco.hust.edu.cn</t>
         </is>
@@ -1428,17 +1435,19 @@
           <t>Institute for Economic and Social Research (IESR)</t>
         </is>
       </c>
-      <c r="F18" s="2" t="n">
-        <v>46357</v>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477972 | https://iesr.jnu.edu.cn/Home/main.htm</t>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1451,7 +1460,7 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>https://iesr.jnu.edu.cn/Home/main.htm</t>
         </is>
@@ -1488,17 +1497,19 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="F19" s="2" t="n">
-        <v>46346</v>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478129 | https://apply.interfolio.com/194759</t>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1511,7 +1522,7 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>https://apply.interfolio.com/194759</t>
         </is>
@@ -1548,17 +1559,19 @@
           <t>Institute of South-South Cooperation and Development (ISSCAD)</t>
         </is>
       </c>
-      <c r="F20" s="2" t="n">
-        <v>46346</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478110 | http://www.nsd.pku.edu.cn</t>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1571,7 +1584,7 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>http://www.nsd.pku.edu.cn</t>
         </is>
@@ -1613,17 +1626,19 @@
           <t>Institute of New Structural Economics (INSE)</t>
         </is>
       </c>
-      <c r="F21" s="2" t="n">
-        <v>46348</v>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-11-22</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477871</t>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1636,7 +1651,7 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477871</t>
         </is>
@@ -1668,17 +1683,19 @@
           <t>985/211</t>
         </is>
       </c>
-      <c r="F22" s="2" t="n">
-        <v>46364</v>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477790 | https://apply.interfolio.com/191920</t>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1691,7 +1708,7 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>https://apply.interfolio.com/191920</t>
         </is>
@@ -1733,17 +1750,19 @@
           <t>School of Finance</t>
         </is>
       </c>
-      <c r="F23" s="2" t="n">
-        <v>46357</v>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477927 | https://docs.qq.com/sheet/DUWVneXFpQkNjR29u?tab=000003</t>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1756,7 +1775,7 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>https://docs.qq.com/sheet/DUWVneXFpQkNjR29u?tab=000003</t>
         </is>
@@ -1793,17 +1812,19 @@
           <t>985/211</t>
         </is>
       </c>
-      <c r="F24" s="2" t="n">
-        <v>46357</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477926 | https://docs.qq.com/sheet/DUWVneXFpQkNjR29u?tab=000003</t>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1816,7 +1837,7 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>https://docs.qq.com/sheet/DUWVneXFpQkNjR29u?tab=000003</t>
         </is>
@@ -1858,17 +1879,19 @@
           <t>Shanghai Advanced Institute of Finance</t>
         </is>
       </c>
-      <c r="F25" s="2" t="n">
-        <v>46355</v>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-11-29</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477869 | https://apply.interfolio.com/190654</t>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1876,7 +1899,7 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>https://apply.interfolio.com/190654</t>
         </is>
@@ -1913,17 +1936,19 @@
           <t>Finance and Economics</t>
         </is>
       </c>
-      <c r="F26" s="2" t="n">
-        <v>46752</v>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2027-12-31</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478009</t>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1936,7 +1961,7 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478009</t>
         </is>
@@ -1968,23 +1993,24 @@
           <t>Southwestern University of Finance and Economics</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>Research Institute of Economics and Management</t>
         </is>
       </c>
-      <c r="F27" s="2" t="n">
-        <v>46346</v>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477954 | https://riem.swufe.edu.cn</t>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1992,7 +2018,7 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>https://riem.swufe.edu.cn</t>
         </is>
@@ -2014,18 +2040,19 @@
           <t>The Chinese University of Hong Kong, Shenzhen</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="F28" s="2" t="n">
-        <v>46418</v>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477649</t>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2038,7 +2065,7 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477649</t>
         </is>
@@ -2070,23 +2097,24 @@
           <t>The Hong Kong University of Science and Technology (Guangzhou)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>Financial Technology Thrust</t>
         </is>
       </c>
-      <c r="F29" s="2" t="n">
-        <v>46418</v>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477623 | https://hkust-gz.edu.cn/</t>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2094,7 +2122,7 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>https://hkust-gz.edu.cn/</t>
         </is>
@@ -2131,17 +2159,19 @@
           <t>985/211</t>
         </is>
       </c>
-      <c r="F30" s="2" t="n">
-        <v>46387</v>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477517</t>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2154,7 +2184,7 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K30" s="3" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477517</t>
         </is>
@@ -2196,17 +2226,19 @@
           <t>PBC School of Finance</t>
         </is>
       </c>
-      <c r="F31" s="2" t="n">
-        <v>46360</v>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478170 | http://www.pbcsf.tsinghua.edu.cn/</t>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2214,7 +2246,7 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>http://www.pbcsf.tsinghua.edu.cn/</t>
         </is>
@@ -2246,23 +2278,24 @@
           <t>Wuhan University</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>Economics and Management School &amp; Institute for Advanced Study at Wuhan University</t>
         </is>
       </c>
-      <c r="F32" s="2" t="n">
-        <v>46336</v>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478087</t>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2275,7 +2308,7 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K32" s="3" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478087</t>
         </is>
@@ -2317,17 +2350,19 @@
           <t>Wang Yanan Institute for Studies in Economics (WISE) &amp; School of Economics</t>
         </is>
       </c>
-      <c r="F33" s="2" t="n">
-        <v>46356</v>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477866</t>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2340,7 +2375,7 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477866</t>
         </is>
@@ -2382,17 +2417,19 @@
           <t>Paula and Gregory Chow Institute for Studies in Economics</t>
         </is>
       </c>
-      <c r="F34" s="2" t="n">
-        <v>46356</v>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478097</t>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2400,7 +2437,7 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K34" s="3" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478097</t>
         </is>
@@ -2437,17 +2474,19 @@
           <t>School of Economics</t>
         </is>
       </c>
-      <c r="F35" s="2" t="n">
-        <v>46348</v>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-11-22</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477844</t>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2460,7 +2499,7 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K35" s="3" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477844</t>
         </is>
@@ -2502,17 +2541,19 @@
           <t>School of Public Finance and Taxation</t>
         </is>
       </c>
-      <c r="F36" s="2" t="n">
-        <v>46418</v>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477969</t>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2525,7 +2566,7 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K36" s="3" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477969</t>
         </is>
@@ -2552,23 +2593,24 @@
           <t>Zhongnan University of Economics and Law</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>Wenlan School of Business</t>
         </is>
       </c>
-      <c r="F37" s="2" t="n">
-        <v>46357</v>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478022</t>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2576,7 +2618,7 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K37" s="3" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478022</t>
         </is>
@@ -2603,23 +2645,24 @@
           <t>Zhongnan University of Economics and Law</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>School of Economics</t>
         </is>
       </c>
-      <c r="F38" s="2" t="n">
-        <v>46366</v>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477804</t>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2632,7 +2675,7 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K38" s="3" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477804</t>
         </is>
@@ -2664,19 +2707,19 @@
           <t>Chinese University of Hong Kong (Shenzhen)</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>School of Management and Economics</t>
         </is>
       </c>
-      <c r="F39" s="2" t="n">
-        <v>46327</v>
-      </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>https://econjobmarket.org/positions/12463</t>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2689,7 +2732,7 @@
           <t>EJM</t>
         </is>
       </c>
-      <c r="K39" s="3" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12463</t>
         </is>
@@ -2721,19 +2764,19 @@
           <t>Duke Kunshan University</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>All departments</t>
         </is>
       </c>
-      <c r="F40" s="2" t="n">
-        <v>46327</v>
-      </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>https://econjobmarket.org/positions/12613</t>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2746,7 +2789,7 @@
           <t>EJM</t>
         </is>
       </c>
-      <c r="K40" s="3" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12613</t>
         </is>
@@ -2778,19 +2821,19 @@
           <t>Duke Kunshan University</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>All departments</t>
         </is>
       </c>
-      <c r="F41" s="2" t="n">
-        <v>46327</v>
-      </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>https://econjobmarket.org/positions/12614</t>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2803,7 +2846,7 @@
           <t>EJM</t>
         </is>
       </c>
-      <c r="K41" s="3" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12614</t>
         </is>
@@ -2835,19 +2878,19 @@
           <t>Duke Kunshan University</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>All departments</t>
         </is>
       </c>
-      <c r="F42" s="2" t="n">
-        <v>46327</v>
-      </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>https://econjobmarket.org/positions/12615</t>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2860,7 +2903,7 @@
           <t>EJM</t>
         </is>
       </c>
-      <c r="K42" s="3" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12615</t>
         </is>
@@ -2892,19 +2935,19 @@
           <t>Hong Kong University of Science and Technology (Guangzhou)</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>Society Hub</t>
         </is>
       </c>
-      <c r="F43" s="2" t="n">
-        <v>46387</v>
-      </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>https://econjobmarket.org/positions/12410</t>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2912,7 +2955,7 @@
           <t>EJM</t>
         </is>
       </c>
-      <c r="K43" s="3" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12410</t>
         </is>
@@ -2954,13 +2997,14 @@
           <t>Institute for Economic and Social Research (IESR)</t>
         </is>
       </c>
-      <c r="F44" s="2" t="n">
-        <v>46387</v>
-      </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>https://econjobmarket.org/positions/12348</t>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2973,7 +3017,7 @@
           <t>EJM</t>
         </is>
       </c>
-      <c r="K44" s="3" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12348</t>
         </is>
@@ -3010,13 +3054,14 @@
           <t>Institute for Economic and Social Research (IESR)</t>
         </is>
       </c>
-      <c r="F45" s="2" t="n">
-        <v>46668</v>
-      </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>https://econjobmarket.org/positions/12784</t>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2027-10-08</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3029,7 +3074,7 @@
           <t>EJM</t>
         </is>
       </c>
-      <c r="K45" s="3" t="inlineStr">
+      <c r="K45" s="2" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12784</t>
         </is>
@@ -3061,19 +3106,19 @@
           <t>Shenzhen University</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>College of Economics</t>
         </is>
       </c>
-      <c r="F46" s="2" t="n">
-        <v>46455</v>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>https://econjobmarket.org/positions/12405</t>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2027-03-09</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3081,7 +3126,7 @@
           <t>EJM</t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12405</t>
         </is>
@@ -3108,16 +3153,14 @@
           <t>Anhui University of Finance and Economics</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>School of Economics</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=D43F9930BDD332A2</t>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3125,7 +3168,7 @@
           <t>CICE</t>
         </is>
       </c>
-      <c r="K47" s="3" t="inlineStr">
+      <c r="K47" s="2" t="inlineStr">
         <is>
           <t>http://www.cicecon.org.cn/careers/detail.html?k=D43F9930BDD332A2</t>
         </is>
@@ -3147,16 +3190,14 @@
           <t>Ant Group Research</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>Full-time Postdoctoral Researcher</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=BE0705D307C4EA24</t>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3164,7 +3205,7 @@
           <t>CICE</t>
         </is>
       </c>
-      <c r="K48" s="3" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>http://www.cicecon.org.cn/careers/detail.html?k=BE0705D307C4EA24</t>
         </is>
@@ -3186,16 +3227,14 @@
           <t>Beijing Institute of Technology</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>School of Management and Economics</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=1D0A7E0E5861506A</t>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3203,7 +3242,7 @@
           <t>CICE</t>
         </is>
       </c>
-      <c r="K49" s="3" t="inlineStr">
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>http://www.cicecon.org.cn/careers/detail.html?k=1D0A7E0E5861506A</t>
         </is>
@@ -3225,16 +3264,14 @@
           <t>Beijing Jiaotong University School of Economics and Management</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>Rolling</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=223BE806CD01DB59</t>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3247,7 +3284,7 @@
           <t>CICE</t>
         </is>
       </c>
-      <c r="K50" s="3" t="inlineStr">
+      <c r="K50" s="2" t="inlineStr">
         <is>
           <t>http://www.cicecon.org.cn/careers/detail.html?k=223BE806CD01DB59</t>
         </is>
@@ -3279,10 +3316,14 @@
           <t>BAY AREA INTERNATIONAL BUSINESS SCHOOL</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=4AC7F281ECBD2BA4</t>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3290,7 +3331,7 @@
           <t>CICE</t>
         </is>
       </c>
-      <c r="K51" s="3" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
         <is>
           <t>http://www.cicecon.org.cn/careers/detail.html?k=4AC7F281ECBD2BA4</t>
         </is>
@@ -3312,16 +3353,14 @@
           <t>Dongbei University of Finance &amp; Economics</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>Dongbei University Of Finance And Economics</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=9058523321C2911A</t>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3329,7 +3368,7 @@
           <t>CICE</t>
         </is>
       </c>
-      <c r="K52" s="3" t="inlineStr">
+      <c r="K52" s="2" t="inlineStr">
         <is>
           <t>http://www.cicecon.org.cn/careers/detail.html?k=9058523321C2911A</t>
         </is>
@@ -3361,10 +3400,14 @@
           <t>Glorious Sun School of Business and Management</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=1CE68DDB85B84365</t>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3372,7 +3415,7 @@
           <t>CICE</t>
         </is>
       </c>
-      <c r="K53" s="3" t="inlineStr">
+      <c r="K53" s="2" t="inlineStr">
         <is>
           <t>http://www.cicecon.org.cn/careers/detail.html?k=1CE68DDB85B84365</t>
         </is>
@@ -3404,13 +3447,14 @@
           <t>School of Economics</t>
         </is>
       </c>
-      <c r="F54" s="2" t="n">
-        <v>46327</v>
-      </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=E968D280DD59D564</t>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3418,7 +3462,7 @@
           <t>CICE</t>
         </is>
       </c>
-      <c r="K54" s="3" t="inlineStr">
+      <c r="K54" s="2" t="inlineStr">
         <is>
           <t>http://www.cicecon.org.cn/careers/detail.html?k=E968D280DD59D564</t>
         </is>
@@ -3455,10 +3499,9 @@
           <t>Rolling</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=E153FEE8CC8E11B5</t>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3466,7 +3509,7 @@
           <t>CICE</t>
         </is>
       </c>
-      <c r="K55" s="3" t="inlineStr">
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t>http://www.cicecon.org.cn/careers/detail.html?k=E153FEE8CC8E11B5</t>
         </is>
@@ -3488,16 +3531,14 @@
           <t>Harbin Institute of Technology</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>School of Management</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3ED8A58471D2F80B</t>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3505,7 +3546,7 @@
           <t>CICE</t>
         </is>
       </c>
-      <c r="K56" s="3" t="inlineStr">
+      <c r="K56" s="2" t="inlineStr">
         <is>
           <t>http://www.cicecon.org.cn/careers/detail.html?k=3ED8A58471D2F80B</t>
         </is>
@@ -3527,16 +3568,19 @@
           <t>Huazhong University of Science and Technology</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>School of Economics, Huazhong University of Science &amp; Technology</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A380FA8882023C78</t>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3549,7 +3593,7 @@
           <t>CICE</t>
         </is>
       </c>
-      <c r="K57" s="3" t="inlineStr">
+      <c r="K57" s="2" t="inlineStr">
         <is>
           <t>http://www.cicecon.org.cn/careers/detail.html?k=A380FA8882023C78</t>
         </is>
@@ -3571,16 +3615,14 @@
           <t>Hunan University</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>School of Economics and Trade</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=38CE3CA2770AB83B</t>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3588,7 +3630,7 @@
           <t>CICE</t>
         </is>
       </c>
-      <c r="K58" s="3" t="inlineStr">
+      <c r="K58" s="2" t="inlineStr">
         <is>
           <t>http://www.cicecon.org.cn/careers/detail.html?k=38CE3CA2770AB83B</t>
         </is>
@@ -3610,16 +3652,19 @@
           <t>Lanzhou University of Finance and Economics</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>the Office of Personnel</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=003923B6EFE42FFF</t>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3627,7 +3672,7 @@
           <t>CICE</t>
         </is>
       </c>
-      <c r="K59" s="3" t="inlineStr">
+      <c r="K59" s="2" t="inlineStr">
         <is>
           <t>http://www.cicecon.org.cn/careers/detail.html?k=003923B6EFE42FFF</t>
         </is>
@@ -3659,10 +3704,14 @@
           <t>College of Finance</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=41CE1E8D1AE20F34</t>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3670,7 +3719,7 @@
           <t>CICE</t>
         </is>
       </c>
-      <c r="K60" s="3" t="inlineStr">
+      <c r="K60" s="2" t="inlineStr">
         <is>
           <t>http://www.cicecon.org.cn/careers/detail.html?k=41CE1E8D1AE20F34</t>
         </is>
@@ -3689,7 +3738,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Nanjing University</t>
+          <t>Peking University</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3699,13 +3748,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Business School</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=5EE87D5DE6734D4D</t>
+          <t>Peking University HSBC Business School</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3713,9 +3766,9 @@
           <t>CICE</t>
         </is>
       </c>
-      <c r="K61" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=5EE87D5DE6734D4D</t>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -3742,16 +3795,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Peking University HSBC Business School</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="n">
-        <v>46364</v>
-      </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
+          <t>Guanghua School of Management</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3759,9 +3813,9 @@
           <t>CICE</t>
         </is>
       </c>
-      <c r="K62" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -3778,7 +3832,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Peking University</t>
+          <t>Renmin University of China</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3788,18 +3842,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Guanghua School of Management</t>
+          <t>School of Finance, Renmin University of China</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rolling</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3807,9 +3860,9 @@
           <t>CICE</t>
         </is>
       </c>
-      <c r="K63" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -3826,26 +3879,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Renmin University of China</t>
+          <t>Shanghai Jiao Tong University</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>985/211</t>
+          <t>211</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>School of Finance, Renmin University of China</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="n">
-        <v>46357</v>
-      </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
+          <t>Antai College of Economics and Management</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-11-15</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3853,9 +3907,9 @@
           <t>CICE</t>
         </is>
       </c>
-      <c r="K64" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -3872,7 +3926,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Shanghai Institute for Mathematics and Interdisciplinary Sciences</t>
+          <t>Shanghai University of Finance and Economics</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3882,18 +3936,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>The Shanghai Institute for Mathematics and Interdisciplinary Sciences</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Rolling</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=D6296C379B46AFF9</t>
+          <t>School of Economics</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3901,9 +3949,9 @@
           <t>CICE</t>
         </is>
       </c>
-      <c r="K65" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=D6296C379B46AFF9</t>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -3920,26 +3968,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Shanghai Jiao Tong University</t>
+          <t>Sun Yat-sen University</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>985/211</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Antai College of Economics and Management</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="n">
-        <v>46341</v>
-      </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
+          <t>Lingnan College</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3947,14 +3996,14 @@
           <t>CICE</t>
         </is>
       </c>
-      <c r="K66" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=73CF283104D9C7BB</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -3966,23 +4015,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Shanghai University of Finance and Economics</t>
+          <t>Tsinghua University</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>985/211</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>School of Economics</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
+          <t>School of Economics and Management</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3990,9 +4043,9 @@
           <t>CICE</t>
         </is>
       </c>
-      <c r="K67" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -4009,7 +4062,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sun Yat-sen University</t>
+          <t>Tsinghua University</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4019,18 +4072,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Lingnan College</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Rolling</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=73CF283104D9C7BB</t>
+          <t>Center for International Finance and Economics Research</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4038,9 +4085,9 @@
           <t>CICE</t>
         </is>
       </c>
-      <c r="K68" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=73CF283104D9C7BB</t>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -4057,26 +4104,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tsinghua University</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>985/211</t>
+          <t>University of Electronic Science and Technology of China</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>School of Economics and Management</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="n">
-        <v>46356</v>
-      </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
+          <t>School of Management and Economics</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4084,14 +4127,14 @@
           <t>CICE</t>
         </is>
       </c>
-      <c r="K69" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -4103,23 +4146,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tsinghua University</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>985/211</t>
+          <t>University of Science and Technology of China</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Center for International Finance and Economics Research</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
+          <t>Institute of International Finance</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4127,9 +4169,9 @@
           <t>CICE</t>
         </is>
       </c>
-      <c r="K70" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -4146,19 +4188,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>University of Electronic Science and Technology of China</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>University of Science and Technology of China</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>School of Management and Economics</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
+          <t>School of Management</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4166,14 +4211,14 @@
           <t>CICE</t>
         </is>
       </c>
-      <c r="K71" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Faculty</t>
         </is>
       </c>
     </row>
@@ -4185,19 +4230,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>University of Science and Technology of China</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>Xi%u2019an Jiaotong University</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Institute of International Finance</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
+          <t>School of Economics and Finance</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4205,14 +4253,14 @@
           <t>CICE</t>
         </is>
       </c>
-      <c r="K72" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Faculty</t>
         </is>
       </c>
     </row>
@@ -4224,19 +4272,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>University of Science and Technology of China</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>Xi%u2019an Jiaotong-Liverpool University</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>School of Management</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
+          <t>International Business School Suzhou (IBSS), Department of Economics</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4244,9 +4295,9 @@
           <t>CICE</t>
         </is>
       </c>
-      <c r="K73" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -4263,19 +4314,27 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Xi%u2019an Jiaotong University</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>Zhejiang University</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>985/211</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>School of Economics and Finance</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
+          <t>School of Economics</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4283,9 +4342,9 @@
           <t>CICE</t>
         </is>
       </c>
-      <c r="K74" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=7D928B7B1C35099A</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -4302,19 +4361,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Xi%u2019an Jiaotong-Liverpool University</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
+          <t>Zhejiang University</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>985/211</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>International Business School Suzhou (IBSS), Department of Economics</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
+          <t>International Business School</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4322,14 +4384,14 @@
           <t>CICE</t>
         </is>
       </c>
-      <c r="K75" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -4341,28 +4403,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Zhejiang University</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>985/211</t>
+          <t>Zhongnan Unviersity of Economics and Law</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>School of Economics</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Rolling</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=7D928B7B1C35099A</t>
+          <t>School of Finance</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4370,9 +4421,9 @@
           <t>CICE</t>
         </is>
       </c>
-      <c r="K76" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=7D928B7B1C35099A</t>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -4384,77 +4435,104 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Kowloon Tong, Kowloon</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Zhejiang University</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>985/211</t>
+          <t>City University of Hong Kong</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>International Business School</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
+          <t>Economics and Finance</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Job Market Paper; Research Statement</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K77" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
+          <t>EJM</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>https://econjobmarket.org/positions/12596</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>efpost@cityu.edu.hk</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Faculty</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Pokfulam Road</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Zhongnan Unviersity of Economics and Law</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>University of Hong Kong</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>School of Finance</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-11-15</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K78" s="3" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
+          <t>EJM</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>https://econjobmarket.org/positions/12521</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>orgecon@hku.hk</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -4471,32 +4549,32 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Kowloon Tong, Kowloon</t>
+          <t>Pokfulam Road</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>City University of Hong Kong</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>University of Hong Kong</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Economics and Finance</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="n">
-        <v>46356</v>
-      </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>https://econjobmarket.org/positions/12596</t>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Job Market Paper; Research Statement</t>
+          <t>Job Market Paper</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4504,14 +4582,14 @@
           <t>EJM</t>
         </is>
       </c>
-      <c r="K79" s="3" t="inlineStr">
-        <is>
-          <t>https://econjobmarket.org/positions/12596</t>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>https://econjobmarket.org/positions/12581</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>efpost@cityu.edu.hk</t>
+          <t>econ.jobmarket@hku.hk</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -4523,47 +4601,52 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Pokfulam Road</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>University of Hong Kong</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>City University of Hong Kong</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Economics</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="n">
-        <v>46341</v>
-      </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>https://econjobmarket.org/positions/12521</t>
+          <t>Department of Economics and Finance</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Job Market Paper; Research Statement</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>EJM</t>
-        </is>
-      </c>
-      <c r="K80" s="3" t="inlineStr">
-        <is>
-          <t>https://econjobmarket.org/positions/12521</t>
+          <t>AEA</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>http://jobs.cityu.edu.hk</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>orgecon@hku.hk</t>
+          <t>efpost@cityu.edu.hk</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -4575,52 +4658,52 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Pokfulam Road</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>University of Hong Kong</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>City University of Hong Kong</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Economics</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="n">
-        <v>46356</v>
-      </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>https://econjobmarket.org/positions/12581</t>
+          <t>Department of Economics and Finance</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Job Market Paper</t>
+          <t>Job Market Paper; Research Statement</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>EJM</t>
-        </is>
-      </c>
-      <c r="K81" s="3" t="inlineStr">
-        <is>
-          <t>https://econjobmarket.org/positions/12581</t>
+          <t>AEA</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>http://jobs.cityu.edu.hk</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>econ.jobmarket@hku.hk</t>
+          <t>efpost@cityu.edu.hk</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -4640,28 +4723,19 @@
           <t>City University of Hong Kong</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Department of Economics and Finance</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="n">
-        <v>46356</v>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477722 | http://jobs.cityu.edu.hk</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Job Market Paper; Research Statement</t>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4669,14 +4743,9 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K82" s="3" t="inlineStr">
-        <is>
-          <t>http://jobs.cityu.edu.hk</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>efpost@cityu.edu.hk</t>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cityu.edu.hk/academic/colleges-schools-and-departments</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -4691,33 +4760,39 @@
           <t>HONG KONG</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Hong Kong, Hong Kong</t>
+        </is>
+      </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>City University of Hong Kong</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>Hong Kong University of Science and Technology</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Department of Economics and Finance</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="n">
-        <v>46356</v>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-11-22</t>
+        </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477723 | http://jobs.cityu.edu.hk</t>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Job Market Paper; Research Statement</t>
+          <t>Research Papers</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4725,14 +4800,14 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K83" s="3" t="inlineStr">
-        <is>
-          <t>http://jobs.cityu.edu.hk</t>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>https://apply.interfolio.com/191029</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>efpost@cityu.edu.hk</t>
+          <t>econjob@ust.hk</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -4749,21 +4824,32 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>City University of Hong Kong</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="F84" s="2" t="n">
-        <v>46418</v>
+          <t>The Chinese University of Hong Kong</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Department of Decisions, Operations and Technology</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477624 | https://www.cityu.edu.hk/academic/colleges-schools-and-departments</t>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Teaching Evaluations</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4771,9 +4857,14 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K84" s="3" t="inlineStr">
-        <is>
-          <t>https://www.cityu.edu.hk/academic/colleges-schools-and-departments</t>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>http://career.cuhk.edu.hk</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>dote@cuhk.edu.hk</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -4788,38 +4879,34 @@
           <t>HONG KONG</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Hong Kong, Hong Kong</t>
-        </is>
-      </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hong Kong University of Science and Technology</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>The University of Hong Kong</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>Economics</t>
         </is>
       </c>
-      <c r="F85" s="2" t="n">
-        <v>46348</v>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477656 | https://apply.interfolio.com/191029</t>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Research Papers</t>
+          <t>Job Market Paper</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4827,14 +4914,14 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K85" s="3" t="inlineStr">
-        <is>
-          <t>https://apply.interfolio.com/191029</t>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hku.hk</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>econjob@ust.hk</t>
+          <t>econ.jobmarket@hku.hk</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -4846,36 +4933,42 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>JAPAN</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Tokyo, Tokyo</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>The Chinese University of Hong Kong</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>Bank of Japan</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Department of Decisions, Operations and Technology</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="n">
-        <v>46387</v>
+          <t>Institute for Monetary and Economic Studies (IMES)</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477636 | http://career.cuhk.edu.hk</t>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Teaching Evaluations</t>
+          <t>Research Papers</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -4883,14 +4976,9 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K86" s="3" t="inlineStr">
-        <is>
-          <t>http://career.cuhk.edu.hk</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>dote@cuhk.edu.hk</t>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477873</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -4902,36 +4990,37 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>JAPAN</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Minato-Ku, Tokyo</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>The University of Hong Kong</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Economics</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="n">
-        <v>46336</v>
+          <t>Japan Fair Trade Commission</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477668 | https://jobs.hku.hk</t>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Job Market Paper</t>
+          <t>Research Papers</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -4939,14 +5028,9 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K87" s="3" t="inlineStr">
-        <is>
-          <t>https://jobs.hku.hk</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>econ.jobmarket@hku.hk</t>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jftc.go.jp/soshiki/recruit/specialty.html</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -4968,31 +5052,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bank of Japan</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
+          <t>Musashi University</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Institute for Monetary and Economic Studies (IMES)</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="n">
-        <v>46356</v>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477873</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Research Papers</t>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5000,9 +5080,9 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K88" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477873</t>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>https://jrecin.jst.go.jp/seek/SeekJorDetail/Changelang?id=D126070158&amp;lang=1</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -5019,31 +5099,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Minato-Ku, Tokyo</t>
+          <t>Yushima, Bunkyo, Tokyo</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Japan Fair Trade Commission</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="F89" s="2" t="n">
-        <v>46418</v>
+          <t>UTokyo Economic Consulting Inc.</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477599 | https://www.jftc.go.jp/soshiki/recruit/specialty.html</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>Research Papers</t>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5051,9 +5127,14 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K89" s="3" t="inlineStr">
-        <is>
-          <t>https://www.jftc.go.jp/soshiki/recruit/specialty.html</t>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>https://utecon.net/en/</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>recruit@utecon.net</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -5070,31 +5151,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tokyo, Tokyo</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Musashi University</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Economics</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="n">
-        <v>46326</v>
+          <t>Waseda University</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477561 | https://jrecin.jst.go.jp/seek/SeekJorDetail/Changelang?id=D126070158&amp;lang=1</t>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5102,9 +5179,9 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K90" s="3" t="inlineStr">
-        <is>
-          <t>https://jrecin.jst.go.jp/seek/SeekJorDetail/Changelang?id=D126070158&amp;lang=1</t>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26944/</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -5121,26 +5198,32 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Yushima, Bunkyo, Tokyo</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>UTokyo Economic Consulting Inc.</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="F91" s="2" t="n">
-        <v>46356</v>
+          <t>Waseda University</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Faculty of Political Science and Economics (FPSE)</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H91" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477714 | https://utecon.net/en/</t>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5148,14 +5231,9 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K91" s="3" t="inlineStr">
-        <is>
-          <t>https://utecon.net/en/</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>recruit@utecon.net</t>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26955/</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -5167,41 +5245,52 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>JAPAN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Kyoto, Kyoto</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Waseda University</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="F92" s="2" t="n">
-        <v>46310</v>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477611 | https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26944/</t>
+          <t>Kyoto University</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Institute for Economic Research</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Research Papers</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>AEA</t>
-        </is>
-      </c>
-      <c r="K92" s="3" t="inlineStr">
-        <is>
-          <t>https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26944/</t>
+          <t>EJM</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>https://econjobmarket.org/positions/12683</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>soumu-jinji@kier.kyoto-u.ac.jp</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -5213,36 +5302,37 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>JAPAN</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Tokyo</t>
+          <t>MACAO; CHINA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Waseda University</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
+          <t>University of Macau (UM)</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Faculty of Political Science and Economics (FPSE)</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="n">
-        <v>46310</v>
+          <t>Department of Finance and Business Economics</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H93" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477612 | https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26955/</t>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>CV; Cover Letter; Job Market Paper; Research Papers; Teaching Evaluations; Letters of Reference</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5250,9 +5340,9 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K93" s="3" t="inlineStr">
-        <is>
-          <t>https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26955/</t>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>https://career.admo.um.edu.mo/learn-more</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -5264,52 +5354,52 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>MALAYSIA</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Kyoto, Kyoto</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Kyoto University</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Institute for Economic Research</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="n">
-        <v>46332</v>
-      </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>https://econjobmarket.org/positions/12683</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>Research Papers</t>
+          <t>The South East Asian Central Banks (SEACEN) Research and Training Centre</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>985/211</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>EJM</t>
-        </is>
-      </c>
-      <c r="K94" s="3" t="inlineStr">
-        <is>
-          <t>https://econjobmarket.org/positions/12683</t>
+          <t>AEA</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seacen.org/</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>soumu-jinji@kier.kyoto-u.ac.jp</t>
+          <t>hr@seacen.org</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -5321,46 +5411,47 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MACAO; CHINA</t>
+          <t>MY</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur, Malaysia</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>University of Macau (UM)</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
+          <t>Asia School of Business</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Department of Finance and Business Economics</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="n">
-        <v>46356</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H95" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477678 | https://career.admo.um.edu.mo/learn-more</t>
+          <t>All departments</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>CV; Cover Letter; Job Market Paper; Research Papers; Teaching Evaluations; Letters of Reference</t>
+          <t>CV; Teaching Statement</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>AEA</t>
-        </is>
-      </c>
-      <c r="K95" s="3" t="inlineStr">
-        <is>
-          <t>https://career.admo.um.edu.mo/learn-more</t>
+          <t>EJM</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>https://econjobmarket.org/positions/12494</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -5372,35 +5463,42 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MALAYSIA</t>
+          <t>NEW ZEALAND</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Auckland, Auckland</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>The South East Asian Central Banks (SEACEN) Research and Training Centre</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="n">
-        <v>46418</v>
+          <t>The University of Auckland</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477702 | https://www.seacen.org/</t>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>CV; Cover Letter; Teaching Evaluations</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -5408,14 +5506,9 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K96" s="3" t="inlineStr">
-        <is>
-          <t>https://www.seacen.org/</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>hr@seacen.org</t>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/TheUniversityOfAuckland/744000151521321-lecturer-senior-lecturer-economics</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -5427,47 +5520,52 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>TAIWAN</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Kuala Lumpur, Malaysia</t>
+          <t>Taipei</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Asia School of Business</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>All departments</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="n">
-        <v>46356</v>
-      </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>https://econjobmarket.org/positions/12494</t>
+          <t>Institute of Economics, Academia Sinica (IEAS)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>CV; Teaching Statement</t>
+          <t>Cover Letter; Job Market Paper</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>EJM</t>
-        </is>
-      </c>
-      <c r="K97" s="3" t="inlineStr">
-        <is>
-          <t>https://econjobmarket.org/positions/12494</t>
+          <t>AEA</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.econ.sinica.edu.tw/</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>searchcommit@econ.sinica.edu.tw</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -5479,41 +5577,42 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>NEW ZEALAND</t>
+          <t>TAIWAN</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Auckland, Auckland</t>
+          <t>Taoyuan</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>The University of Auckland</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
+          <t>National Central University</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>Economics</t>
         </is>
       </c>
-      <c r="F98" s="2" t="n">
-        <v>46321</v>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478084 | https://jobs.smartrecruiters.com/TheUniversityOfAuckland/744000151521321-lecturer-senior-lecturer-economics</t>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>CV; Cover Letter; Teaching Evaluations</t>
+          <t>CV; Cover Letter; Job Market Paper; Transcript</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -5521,9 +5620,14 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K98" s="3" t="inlineStr">
-        <is>
-          <t>https://jobs.smartrecruiters.com/TheUniversityOfAuckland/744000151521321-lecturer-senior-lecturer-economics</t>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477598</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>ncu66301@ncu.edu.tw</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -5540,31 +5644,32 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Taipei</t>
+          <t>Zhongli, Taoyuan</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Institute of Economics, Academia Sinica (IEAS)</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="F99" s="2" t="n">
-        <v>46357</v>
+          <t>National Central University</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Graduate Institute of Industrial Economics</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-12-12</t>
+        </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H99" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477843 | https://www.econ.sinica.edu.tw/</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>Cover Letter; Job Market Paper</t>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5572,14 +5677,9 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K99" s="3" t="inlineStr">
-        <is>
-          <t>https://www.econ.sinica.edu.tw/</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>searchcommit@econ.sinica.edu.tw</t>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477690</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -5596,7 +5696,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Taoyuan</t>
+          <t>Taoyuan City</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5604,28 +5704,29 @@
           <t>National Central University</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Economics</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="n">
-        <v>46358</v>
+          <t>Department of Finance</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2027-01-15</t>
+        </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477598</t>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>CV; Cover Letter; Job Market Paper; Transcript</t>
+          <t>Job Market Paper</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5633,14 +5734,14 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K100" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477598</t>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477637</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>ncu66301@ncu.edu.tw</t>
+          <t>ncu6250@ncu.edu.tw</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -5657,31 +5758,37 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Zhongli, Taoyuan</t>
+          <t>Tainan</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>National Central University</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
+          <t>National Cheng Kung University</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Graduate Institute of Industrial Economics</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="n">
-        <v>46368</v>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-11-28</t>
+        </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477690</t>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Cover Letter</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -5689,9 +5796,9 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K101" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477690</t>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477925</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -5708,36 +5815,32 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Taoyuan City</t>
+          <t>Taipei</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>National Central University</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
+          <t>National Chengchi University</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Department of Finance</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="n">
-        <v>46402</v>
+          <t>Department of Economics</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477637</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>Job Market Paper</t>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -5745,14 +5848,14 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K102" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477637</t>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477745</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>ncu6250@ncu.edu.tw</t>
+          <t>econ@nccu.edu.tw</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -5769,36 +5872,37 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Tainan</t>
+          <t>Taipei</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>National Cheng Kung University</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>National Chengchi University</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Economics</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="n">
-        <v>46354</v>
+          <t>College of Global Banking and Finance</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H103" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477925</t>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Cover Letter</t>
+          <t>CV; Job Market Paper</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -5806,9 +5910,14 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K103" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477925</t>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>https://cgbf.nccu.edu.tw/</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>pthung@mail3.nccu.tw</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -5833,23 +5942,29 @@
           <t>National Chengchi University</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Department of Economics</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="n">
-        <v>46356</v>
+          <t>Department of Money and Banking</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477745</t>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>CV; Cover Letter; Job Market Paper</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -5857,14 +5972,14 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K104" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477745</t>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478008</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>econ@nccu.edu.tw</t>
+          <t>banking@nccu.edu.tw</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -5889,28 +6004,29 @@
           <t>National Chengchi University</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>College of Global Banking and Finance</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="n">
-        <v>46387</v>
+          <t>The Department of International Business</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2027-03-12</t>
+        </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H105" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477791 | https://cgbf.nccu.edu.tw/</t>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>CV; Job Market Paper</t>
+          <t>CV; Cover Letter; Job Market Paper</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -5918,14 +6034,9 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K105" s="3" t="inlineStr">
-        <is>
-          <t>https://cgbf.nccu.edu.tw/</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>pthung@mail3.nccu.tw</t>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478133</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -5942,36 +6053,37 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Taipei</t>
+          <t>Minhsiung, CHIAYI</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>National Chengchi University</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>National Chung Cheng University</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Department of Money and Banking</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="n">
-        <v>46418</v>
+          <t>Department of Economics</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478008</t>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>CV; Cover Letter; Job Market Paper</t>
+          <t>Cover Letter; Research Papers; Research Statement; Transcript</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -5979,14 +6091,9 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K106" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478008</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>banking@nccu.edu.tw</t>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477555</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -6003,36 +6110,42 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Taipei</t>
+          <t>Kaohsiung</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>National Chengchi University</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>National Sun Yat-sen University</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>985/211</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>The Department of International Business</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="n">
-        <v>46458</v>
+          <t>Department of Political Economy</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H107" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478133</t>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>CV; Cover Letter; Job Market Paper</t>
+          <t>Cover Letter; Job Market Paper; Teaching Statement; Research Statement</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6040,9 +6153,14 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K107" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478133</t>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477532</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>poleco@mail.nsysu.edu.tw</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -6059,36 +6177,32 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Minhsiung, CHIAYI</t>
+          <t>New Taipei City</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>National Chung Cheng University</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>National Taipei University</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>Department of Economics</t>
         </is>
       </c>
-      <c r="F108" s="2" t="n">
-        <v>46418</v>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477555</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>Cover Letter; Research Papers; Research Statement; Transcript</t>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -6096,9 +6210,14 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K108" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477555</t>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477648</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>econ_job@mail.ntpu.edu.tw; tapply@gm.ntpu.edu.tw</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -6115,40 +6234,32 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Kaohsiung</t>
+          <t>Taipei</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>National Sun Yat-sen University</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>985/211</t>
+          <t>National Taiwan University</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Department of Political Economy</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="n">
-        <v>46387</v>
+          <t>Department of Economics</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H109" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477532</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>Cover Letter; Job Market Paper; Teaching Statement; Research Statement</t>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6156,14 +6267,14 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K109" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477532</t>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>https://econ.ntu.edu.tw</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>poleco@mail.nsysu.edu.tw</t>
+          <t>kuanmingchen@ntu.edu.tw</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -6180,31 +6291,37 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>New Taipei City</t>
+          <t>Hsinchu</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>National Taipei University</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>National Tsing Hua University</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>985/211</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Department of Economics</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="n">
-        <v>46366</v>
+          <t>Taipei School of Economics and Political Science (TSE)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-11-15</t>
+        </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H110" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477648</t>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6212,14 +6329,14 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K110" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477648</t>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tse.nthu.edu.tw/</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>econ_job@mail.ntpu.edu.tw; tapply@gm.ntpu.edu.tw</t>
+          <t>tse@my.nthu.edu.tw</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -6236,31 +6353,37 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Taipei</t>
+          <t>Hsinchu City, Hsinchu</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>National Taiwan University</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>National Tsing Hua University</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>985/211</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Department of Economics</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="n">
-        <v>46418</v>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-11-29</t>
+        </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H111" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477929 | https://econ.ntu.edu.tw</t>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6268,132 +6391,12 @@
           <t>AEA</t>
         </is>
       </c>
-      <c r="K111" s="3" t="inlineStr">
-        <is>
-          <t>https://econ.ntu.edu.tw</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>kuanmingchen@ntu.edu.tw</t>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477989</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>TAIWAN</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Hsinchu</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>National Tsing Hua University</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Taipei School of Economics and Political Science (TSE)</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="n">
-        <v>46341</v>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H112" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477721 | https://www.tse.nthu.edu.tw/</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>AEA</t>
-        </is>
-      </c>
-      <c r="K112" s="3" t="inlineStr">
-        <is>
-          <t>https://www.tse.nthu.edu.tw/</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>tse@my.nthu.edu.tw</t>
-        </is>
-      </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>TAIWAN</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Hsinchu City, Hsinchu</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>National Tsing Hua University</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Economics</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="n">
-        <v>46355</v>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H113" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477989</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>AEA</t>
-        </is>
-      </c>
-      <c r="K113" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477989</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
@@ -6621,10 +6624,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId218"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId219"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId224"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
